--- a/CHIK_MORBID/03_Output/tables/brazil_profile_burden_allocation_PROTOTYPE.xlsx
+++ b/CHIK_MORBID/03_Output/tables/brazil_profile_burden_allocation_PROTOTYPE.xlsx
@@ -12,9 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t xml:space="preserve">age_start10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">age_band</t>
   </si>
   <si>
     <t xml:space="preserve">profile</t>
@@ -29,10 +32,28 @@
     <t xml:space="preserve">allocated_hosp</t>
   </si>
   <si>
-    <t xml:space="preserve">allocated_hosp_lo</t>
+    <t xml:space="preserve">allocated_hosp_median</t>
   </si>
   <si>
-    <t xml:space="preserve">allocated_hosp_hi</t>
+    <t xml:space="preserve">allocated_hosp_lower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">allocated_hosp_upper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hosp_rate_100k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hosp_rate_100k_median</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hosp_rate_100k_lower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hosp_rate_100k_upper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">symptomatic_profile</t>
   </si>
   <si>
     <t xml:space="preserve">total_hosp</t>
@@ -44,13 +65,31 @@
     <t xml:space="preserve">allocated_death</t>
   </si>
   <si>
-    <t xml:space="preserve">allocated_death_lo</t>
+    <t xml:space="preserve">allocated_death_median</t>
   </si>
   <si>
-    <t xml:space="preserve">allocated_death_hi</t>
+    <t xml:space="preserve">allocated_death_lower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">allocated_death_upper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">death_rate_100k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">death_rate_100k_median</t>
+  </si>
+  <si>
+    <t xml:space="preserve">death_rate_100k_lower</t>
+  </si>
+  <si>
+    <t xml:space="preserve">death_rate_100k_upper</t>
   </si>
   <si>
     <t xml:space="preserve">total_death</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0-9</t>
   </si>
   <si>
     <t xml:space="preserve">None</t>
@@ -75,6 +114,30 @@
   </si>
   <si>
     <t xml:space="preserve">DM+HTN+CKD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30-39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40-49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50-59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60-69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70-79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80-89</t>
   </si>
 </sst>
 </file>
@@ -122,22 +185,34 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:M73" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:M73"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:Y73" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:Y73"/>
+  <tableColumns count="25">
     <tableColumn id="1" name="age_start10"/>
-    <tableColumn id="2" name="profile"/>
-    <tableColumn id="3" name="pi_point"/>
-    <tableColumn id="4" name="rr_hosp"/>
-    <tableColumn id="5" name="allocated_hosp"/>
-    <tableColumn id="6" name="allocated_hosp_lo"/>
-    <tableColumn id="7" name="allocated_hosp_hi"/>
-    <tableColumn id="8" name="total_hosp"/>
-    <tableColumn id="9" name="rr_death"/>
-    <tableColumn id="10" name="allocated_death"/>
-    <tableColumn id="11" name="allocated_death_lo"/>
-    <tableColumn id="12" name="allocated_death_hi"/>
-    <tableColumn id="13" name="total_death"/>
+    <tableColumn id="2" name="age_band"/>
+    <tableColumn id="3" name="profile"/>
+    <tableColumn id="4" name="pi_point"/>
+    <tableColumn id="5" name="rr_hosp"/>
+    <tableColumn id="6" name="allocated_hosp"/>
+    <tableColumn id="7" name="allocated_hosp_median"/>
+    <tableColumn id="8" name="allocated_hosp_lower"/>
+    <tableColumn id="9" name="allocated_hosp_upper"/>
+    <tableColumn id="10" name="hosp_rate_100k"/>
+    <tableColumn id="11" name="hosp_rate_100k_median"/>
+    <tableColumn id="12" name="hosp_rate_100k_lower"/>
+    <tableColumn id="13" name="hosp_rate_100k_upper"/>
+    <tableColumn id="14" name="symptomatic_profile"/>
+    <tableColumn id="15" name="total_hosp"/>
+    <tableColumn id="16" name="rr_death"/>
+    <tableColumn id="17" name="allocated_death"/>
+    <tableColumn id="18" name="allocated_death_median"/>
+    <tableColumn id="19" name="allocated_death_lower"/>
+    <tableColumn id="20" name="allocated_death_upper"/>
+    <tableColumn id="21" name="death_rate_100k"/>
+    <tableColumn id="22" name="death_rate_100k_median"/>
+    <tableColumn id="23" name="death_rate_100k_lower"/>
+    <tableColumn id="24" name="death_rate_100k_upper"/>
+    <tableColumn id="25" name="total_death"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -426,18 +501,30 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="11.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="11.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="8.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="17.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="17.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="11.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="11.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="15.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="18.71" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="18.71" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="11.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="21.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="20.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="20.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="14.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="21.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="20.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="20.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="19.71" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="11.71" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="11.71" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="15.71" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="22.71" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="21.71" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="21.71" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="15.71" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="22.71" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="21.71" hidden="0" customWidth="1"/>
+    <col min="24" max="24" width="21.71" hidden="0" customWidth="1"/>
+    <col min="25" max="25" width="11.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,45 +567,117 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="n">
         <v>0.998752812337153</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>6834.58503447087</v>
       </c>
-      <c r="F2" t="n">
-        <v>6838.69266707171</v>
-      </c>
       <c r="G2" t="n">
-        <v>6829.55064283977</v>
+        <v>6834.60637504418</v>
       </c>
       <c r="H2" t="n">
+        <v>6830.99653396836</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6837.73875358344</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3960.6262817724</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3960.64429213003</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3958.5643730911</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3962.44333807959</v>
+      </c>
+      <c r="N2" t="n">
+        <v>172563.239958413</v>
+      </c>
+      <c r="O2" t="n">
         <v>6858.63516598761</v>
       </c>
-      <c r="I2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="n">
+      <c r="Q2" t="n">
         <v>170.364880458316</v>
       </c>
-      <c r="K2" t="n">
-        <v>171.11267500192</v>
-      </c>
-      <c r="L2" t="n">
-        <v>169.048534519727</v>
-      </c>
-      <c r="M2" t="n">
+      <c r="R2" t="n">
+        <v>170.333653449246</v>
+      </c>
+      <c r="S2" t="n">
+        <v>169.381420336748</v>
+      </c>
+      <c r="T2" t="n">
+        <v>171.008533480777</v>
+      </c>
+      <c r="U2" t="n">
+        <v>98.7260557343348</v>
+      </c>
+      <c r="V2" t="n">
+        <v>98.7081574877022</v>
+      </c>
+      <c r="W2" t="n">
+        <v>98.1566967860601</v>
+      </c>
+      <c r="X2" t="n">
+        <v>99.0989652561494</v>
+      </c>
+      <c r="Y2" t="n">
         <v>171.984882694925</v>
       </c>
     </row>
@@ -527,39 +686,75 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="n">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="n">
         <v>0.000134194751703553</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>1.73620391549785</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>1.5943747155099</v>
       </c>
-      <c r="F3" t="n">
-        <v>1.38360076990903</v>
-      </c>
       <c r="G3" t="n">
-        <v>1.79970101163155</v>
+        <v>1.58798114145768</v>
       </c>
       <c r="H3" t="n">
+        <v>1.44191014674756</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.74377802752981</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6876.45485823695</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6854.0724573522</v>
+      </c>
+      <c r="L3" t="n">
+        <v>6261.42774101611</v>
+      </c>
+      <c r="M3" t="n">
+        <v>7396.23233661828</v>
+      </c>
+      <c r="N3" t="n">
+        <v>23.1859984305732</v>
+      </c>
+      <c r="O3" t="n">
         <v>6858.63516598761</v>
       </c>
-      <c r="I3" t="n">
+      <c r="P3" t="n">
         <v>3.87720798284478</v>
       </c>
-      <c r="J3" t="n">
+      <c r="Q3" t="n">
         <v>0.0887517013159708</v>
       </c>
-      <c r="K3" t="n">
-        <v>0.0637284430541108</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.121034965544164</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="R3" t="n">
+        <v>0.0874888446356879</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.0663207281577334</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.117675897553632</v>
+      </c>
+      <c r="U3" t="n">
+        <v>382.781451407942</v>
+      </c>
+      <c r="V3" t="n">
+        <v>379.022471819103</v>
+      </c>
+      <c r="W3" t="n">
+        <v>286.76852674307</v>
+      </c>
+      <c r="X3" t="n">
+        <v>508.777518370379</v>
+      </c>
+      <c r="Y3" t="n">
         <v>171.984882694925</v>
       </c>
     </row>
@@ -568,16 +763,16 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="n">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>1.52453466418204</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -586,21 +781,41 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
         <v>6858.63516598761</v>
       </c>
-      <c r="I4" t="n">
+      <c r="P4" t="n">
         <v>2.54503453199424</v>
       </c>
-      <c r="J4" t="n">
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
+      <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
+      <c r="S4" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="n">
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4"/>
+      <c r="V4"/>
+      <c r="W4"/>
+      <c r="X4"/>
+      <c r="Y4" t="n">
         <v>171.984882694925</v>
       </c>
     </row>
@@ -609,39 +824,75 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="n">
         <v>0.00103440959721557</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>2.89604955563333</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>20.4999436044572</v>
       </c>
-      <c r="F5" t="n">
-        <v>17.2789644229585</v>
-      </c>
       <c r="G5" t="n">
-        <v>24.3353192337603</v>
+        <v>20.5334141124993</v>
       </c>
       <c r="H5" t="n">
+        <v>17.3835726948529</v>
+      </c>
+      <c r="I5" t="n">
+        <v>23.8755566843296</v>
+      </c>
+      <c r="J5" t="n">
+        <v>11470.1699833567</v>
+      </c>
+      <c r="K5" t="n">
+        <v>11478.0831021819</v>
+      </c>
+      <c r="L5" t="n">
+        <v>9727.75161973171</v>
+      </c>
+      <c r="M5" t="n">
+        <v>13343.5080449697</v>
+      </c>
+      <c r="N5" t="n">
+        <v>178.723973874867</v>
+      </c>
+      <c r="O5" t="n">
         <v>6858.63516598761</v>
       </c>
-      <c r="I5" t="n">
+      <c r="P5" t="n">
         <v>7.90435131698919</v>
       </c>
-      <c r="J5" t="n">
+      <c r="Q5" t="n">
         <v>1.39470010485544</v>
       </c>
-      <c r="K5" t="n">
-        <v>0.759827948440048</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2.43965513992579</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="R5" t="n">
+        <v>1.40594804861321</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.772935942997172</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.33688241898274</v>
+      </c>
+      <c r="U5" t="n">
+        <v>780.365428664838</v>
+      </c>
+      <c r="V5" t="n">
+        <v>787.866780488822</v>
+      </c>
+      <c r="W5" t="n">
+        <v>434.253881496041</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1305.83762403436</v>
+      </c>
+      <c r="Y5" t="n">
         <v>171.984882694925</v>
       </c>
     </row>
@@ -650,16 +901,16 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="n">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>2.06769736454035</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -668,21 +919,41 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6"/>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
         <v>6858.63516598761</v>
       </c>
-      <c r="I6" t="n">
+      <c r="P6" t="n">
         <v>5.03462423827642</v>
       </c>
-      <c r="J6" t="n">
+      <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
+      <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
+      <c r="S6" t="n">
         <v>0</v>
       </c>
-      <c r="M6" t="n">
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6"/>
+      <c r="V6"/>
+      <c r="W6"/>
+      <c r="X6"/>
+      <c r="Y6" t="n">
         <v>171.984882694925</v>
       </c>
     </row>
@@ -691,39 +962,75 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="n">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="n">
         <v>0.0000785833139283026</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>3.63699661366556</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>1.9558131967726</v>
       </c>
-      <c r="F7" t="n">
-        <v>1.27993372302827</v>
-      </c>
       <c r="G7" t="n">
-        <v>2.94950290244593</v>
+        <v>1.94489785336644</v>
       </c>
       <c r="H7" t="n">
+        <v>1.37977056286451</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.76120977005352</v>
+      </c>
+      <c r="J7" t="n">
+        <v>14404.7843748011</v>
+      </c>
+      <c r="K7" t="n">
+        <v>14315.6293473675</v>
+      </c>
+      <c r="L7" t="n">
+        <v>10235.6290262432</v>
+      </c>
+      <c r="M7" t="n">
+        <v>19750.7506014634</v>
+      </c>
+      <c r="N7" t="n">
+        <v>13.5775249797837</v>
+      </c>
+      <c r="O7" t="n">
         <v>6858.63516598761</v>
       </c>
-      <c r="I7" t="n">
+      <c r="P7" t="n">
         <v>10.1868679468459</v>
       </c>
-      <c r="J7" t="n">
+      <c r="Q7" t="n">
         <v>0.136550430437446</v>
       </c>
-      <c r="K7" t="n">
-        <v>0.0486513015108387</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.375658069728311</v>
-      </c>
-      <c r="M7" t="n">
+      <c r="R7" t="n">
+        <v>0.138370558708848</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.0531254341685007</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.331046642373616</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1005.70929267862</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1004.73000459927</v>
+      </c>
+      <c r="W7" t="n">
+        <v>379.583975335085</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2461.82194243096</v>
+      </c>
+      <c r="Y7" t="n">
         <v>171.984882694925</v>
       </c>
     </row>
@@ -732,16 +1039,16 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" t="n">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>4.52251927826614</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -750,21 +1057,41 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8"/>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>6858.63516598761</v>
       </c>
-      <c r="I8" t="n">
+      <c r="P8" t="n">
         <v>12.1408452842106</v>
       </c>
-      <c r="J8" t="n">
+      <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
+      <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="n">
+      <c r="S8" t="n">
         <v>0</v>
       </c>
-      <c r="M8" t="n">
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8"/>
+      <c r="V8"/>
+      <c r="W8"/>
+      <c r="X8"/>
+      <c r="Y8" t="n">
         <v>171.984882694925</v>
       </c>
     </row>
@@ -773,16 +1100,16 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" t="n">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>3.62093598924897</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -791,21 +1118,41 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9"/>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
         <v>6858.63516598761</v>
       </c>
-      <c r="I9" t="n">
+      <c r="P9" t="n">
         <v>15.7071764801393</v>
       </c>
-      <c r="J9" t="n">
+      <c r="Q9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="n">
+      <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="n">
+      <c r="S9" t="n">
         <v>0</v>
       </c>
-      <c r="M9" t="n">
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9"/>
+      <c r="V9"/>
+      <c r="W9"/>
+      <c r="X9"/>
+      <c r="Y9" t="n">
         <v>171.984882694925</v>
       </c>
     </row>
@@ -814,39 +1161,75 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" t="n">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="n">
         <v>0.946504717483323</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>1</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>5722.6118088708</v>
       </c>
-      <c r="F10" t="n">
-        <v>5821.37270953234</v>
-      </c>
       <c r="G10" t="n">
-        <v>5612.63311137329</v>
+        <v>5723.73062905913</v>
       </c>
       <c r="H10" t="n">
+        <v>5675.32829755969</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5770.93869078507</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3705.35695976885</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3706.00116388639</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3673.94162271062</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3736.04198266133</v>
+      </c>
+      <c r="N10" t="n">
+        <v>154441.579340518</v>
+      </c>
+      <c r="O10" t="n">
         <v>6477.22348854156</v>
       </c>
-      <c r="I10" t="n">
+      <c r="P10" t="n">
         <v>1</v>
       </c>
-      <c r="J10" t="n">
+      <c r="Q10" t="n">
         <v>88.2621289426937</v>
       </c>
-      <c r="K10" t="n">
-        <v>96.8766331711694</v>
-      </c>
-      <c r="L10" t="n">
-        <v>76.8938391126991</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="R10" t="n">
+        <v>88.0469367108195</v>
+      </c>
+      <c r="S10" t="n">
+        <v>81.3530760973307</v>
+      </c>
+      <c r="T10" t="n">
+        <v>93.3234916917418</v>
+      </c>
+      <c r="U10" t="n">
+        <v>57.1492012187279</v>
+      </c>
+      <c r="V10" t="n">
+        <v>56.9954673392012</v>
+      </c>
+      <c r="W10" t="n">
+        <v>52.6724462316885</v>
+      </c>
+      <c r="X10" t="n">
+        <v>60.4021966539118</v>
+      </c>
+      <c r="Y10" t="n">
         <v>116.15967753879</v>
       </c>
     </row>
@@ -855,39 +1238,75 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" t="n">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" t="n">
         <v>0.00207956504525322</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>1.73620391549785</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>21.8295480350433</v>
       </c>
-      <c r="F11" t="n">
-        <v>19.2706900700051</v>
-      </c>
       <c r="G11" t="n">
-        <v>24.1690731411065</v>
+        <v>21.7486000594766</v>
       </c>
       <c r="H11" t="n">
+        <v>19.7423231063804</v>
+      </c>
+      <c r="I11" t="n">
+        <v>23.8474265354337</v>
+      </c>
+      <c r="J11" t="n">
+        <v>6433.2552618679</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6411.48027006444</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5858.8028840326</v>
+      </c>
+      <c r="M11" t="n">
+        <v>6906.78274153667</v>
+      </c>
+      <c r="N11" t="n">
+        <v>339.323517355739</v>
+      </c>
+      <c r="O11" t="n">
         <v>6477.22348854156</v>
       </c>
-      <c r="I11" t="n">
+      <c r="P11" t="n">
         <v>3.87720798284478</v>
       </c>
-      <c r="J11" t="n">
+      <c r="Q11" t="n">
         <v>0.751870807433937</v>
       </c>
-      <c r="K11" t="n">
-        <v>0.590342863734736</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.89965520364655</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="R11" t="n">
+        <v>0.738089617504177</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.552054750768933</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.993808423237228</v>
+      </c>
+      <c r="U11" t="n">
+        <v>221.579339178455</v>
+      </c>
+      <c r="V11" t="n">
+        <v>217.902888548667</v>
+      </c>
+      <c r="W11" t="n">
+        <v>163.584787523172</v>
+      </c>
+      <c r="X11" t="n">
+        <v>290.336531306979</v>
+      </c>
+      <c r="Y11" t="n">
         <v>116.15967753879</v>
       </c>
     </row>
@@ -896,39 +1315,75 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" t="n">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="n">
         <v>0.0279578197052867</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>1.52453466418204</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>257.698628571647</v>
       </c>
-      <c r="F12" t="n">
-        <v>246.815913162302</v>
-      </c>
       <c r="G12" t="n">
-        <v>266.983430315276</v>
+        <v>257.166662990238</v>
       </c>
       <c r="H12" t="n">
+        <v>247.031472282308</v>
+      </c>
+      <c r="I12" t="n">
+        <v>268.284023568384</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5648.94512833579</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5645.83035063658</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5426.58675123843</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5854.46476233057</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4561.88939203887</v>
+      </c>
+      <c r="O12" t="n">
         <v>6477.22348854156</v>
       </c>
-      <c r="I12" t="n">
+      <c r="P12" t="n">
         <v>2.54503453199424</v>
       </c>
-      <c r="J12" t="n">
+      <c r="Q12" t="n">
         <v>6.63511714852886</v>
       </c>
-      <c r="K12" t="n">
-        <v>6.00000388098564</v>
-      </c>
-      <c r="L12" t="n">
-        <v>6.92940607612274</v>
-      </c>
-      <c r="M12" t="n">
+      <c r="R12" t="n">
+        <v>6.54650315708204</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5.57115443279877</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7.66076306664685</v>
+      </c>
+      <c r="U12" t="n">
+        <v>145.44669057755</v>
+      </c>
+      <c r="V12" t="n">
+        <v>143.624303248986</v>
+      </c>
+      <c r="W12" t="n">
+        <v>122.222557603202</v>
+      </c>
+      <c r="X12" t="n">
+        <v>167.558509091261</v>
+      </c>
+      <c r="Y12" t="n">
         <v>116.15967753879</v>
       </c>
     </row>
@@ -937,39 +1392,75 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
+        <v>34</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" t="n">
         <v>0.0159417992832221</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>2.89604955563333</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>279.135343667131</v>
       </c>
-      <c r="F13" t="n">
-        <v>232.819250326976</v>
-      </c>
       <c r="G13" t="n">
-        <v>332.98490799161</v>
+        <v>279.467878194237</v>
       </c>
       <c r="H13" t="n">
+        <v>237.272355016357</v>
+      </c>
+      <c r="I13" t="n">
+        <v>323.988325716978</v>
+      </c>
+      <c r="J13" t="n">
+        <v>10730.8973768015</v>
+      </c>
+      <c r="K13" t="n">
+        <v>10734.7743231952</v>
+      </c>
+      <c r="L13" t="n">
+        <v>9152.77093705276</v>
+      </c>
+      <c r="M13" t="n">
+        <v>12415.784702364</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2601.2302034551</v>
+      </c>
+      <c r="O13" t="n">
         <v>6477.22348854156</v>
       </c>
-      <c r="I13" t="n">
+      <c r="P13" t="n">
         <v>7.90435131698919</v>
       </c>
-      <c r="J13" t="n">
+      <c r="Q13" t="n">
         <v>11.75046862751</v>
       </c>
-      <c r="K13" t="n">
-        <v>6.80927662530602</v>
-      </c>
-      <c r="L13" t="n">
-        <v>18.4765785720561</v>
-      </c>
-      <c r="M13" t="n">
+      <c r="R13" t="n">
+        <v>11.7904087740927</v>
+      </c>
+      <c r="S13" t="n">
+        <v>6.74127236365567</v>
+      </c>
+      <c r="T13" t="n">
+        <v>18.5721169807097</v>
+      </c>
+      <c r="U13" t="n">
+        <v>451.727363918133</v>
+      </c>
+      <c r="V13" t="n">
+        <v>456.676576178698</v>
+      </c>
+      <c r="W13" t="n">
+        <v>262.594989687206</v>
+      </c>
+      <c r="X13" t="n">
+        <v>718.646341755629</v>
+      </c>
+      <c r="Y13" t="n">
         <v>116.15967753879</v>
       </c>
     </row>
@@ -978,39 +1469,75 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" t="n">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="n">
         <v>0.000131767298430106</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>2.06769736454035</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>1.64727504754894</v>
       </c>
-      <c r="F14" t="n">
-        <v>1.5071973160422</v>
-      </c>
       <c r="G14" t="n">
-        <v>1.77961304269997</v>
+        <v>1.6411221805532</v>
       </c>
       <c r="H14" t="n">
+        <v>1.5314506397653</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.76062635312262</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7661.55682039529</v>
+      </c>
+      <c r="K14" t="n">
+        <v>7649.7248886037</v>
+      </c>
+      <c r="L14" t="n">
+        <v>7267.73210152886</v>
+      </c>
+      <c r="M14" t="n">
+        <v>8066.63557598359</v>
+      </c>
+      <c r="N14" t="n">
+        <v>21.5005264095131</v>
+      </c>
+      <c r="O14" t="n">
         <v>6477.22348854156</v>
       </c>
-      <c r="I14" t="n">
+      <c r="P14" t="n">
         <v>5.03462423827642</v>
       </c>
-      <c r="J14" t="n">
+      <c r="Q14" t="n">
         <v>0.0618623366460728</v>
       </c>
-      <c r="K14" t="n">
-        <v>0.0535233793637308</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.0676865756248176</v>
-      </c>
-      <c r="M14" t="n">
+      <c r="R14" t="n">
+        <v>0.0609620390585106</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.051490640442988</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.0729592827141901</v>
+      </c>
+      <c r="U14" t="n">
+        <v>287.724753653944</v>
+      </c>
+      <c r="V14" t="n">
+        <v>283.806150159314</v>
+      </c>
+      <c r="W14" t="n">
+        <v>241.564797822846</v>
+      </c>
+      <c r="X14" t="n">
+        <v>338.466547724888</v>
+      </c>
+      <c r="Y14" t="n">
         <v>116.15967753879</v>
       </c>
     </row>
@@ -1019,39 +1546,75 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" t="n">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" t="n">
         <v>0.000248111436153176</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>3.63699661366556</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>5.45583444183923</v>
       </c>
-      <c r="F15" t="n">
-        <v>3.66718123287784</v>
-      </c>
       <c r="G15" t="n">
-        <v>7.98012651176056</v>
+        <v>5.40869677863395</v>
       </c>
       <c r="H15" t="n">
+        <v>3.87978639384897</v>
+      </c>
+      <c r="I15" t="n">
+        <v>7.61204619656037</v>
+      </c>
+      <c r="J15" t="n">
+        <v>13476.3707151014</v>
+      </c>
+      <c r="K15" t="n">
+        <v>13403.1176300328</v>
+      </c>
+      <c r="L15" t="n">
+        <v>9589.88009061333</v>
+      </c>
+      <c r="M15" t="n">
+        <v>18506.9428799229</v>
+      </c>
+      <c r="N15" t="n">
+        <v>40.4844490937422</v>
+      </c>
+      <c r="O15" t="n">
         <v>6477.22348854156</v>
       </c>
-      <c r="I15" t="n">
+      <c r="P15" t="n">
         <v>10.1868679468459</v>
       </c>
-      <c r="J15" t="n">
+      <c r="Q15" t="n">
         <v>0.235688870340178</v>
       </c>
-      <c r="K15" t="n">
-        <v>0.0927094259945839</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.56254760667965</v>
-      </c>
-      <c r="M15" t="n">
+      <c r="R15" t="n">
+        <v>0.236214090962537</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.0915875696106122</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.566731101614755</v>
+      </c>
+      <c r="U15" t="n">
+        <v>582.171366082906</v>
+      </c>
+      <c r="V15" t="n">
+        <v>578.092438587299</v>
+      </c>
+      <c r="W15" t="n">
+        <v>229.575265023617</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1416.75721363187</v>
+      </c>
+      <c r="Y15" t="n">
         <v>116.15967753879</v>
       </c>
     </row>
@@ -1060,39 +1623,75 @@
         <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" t="n">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="n">
         <v>0.00598355394483713</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>4.52251927826614</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>163.610488531805</v>
       </c>
-      <c r="F16" t="n">
-        <v>131.528121866008</v>
-      </c>
       <c r="G16" t="n">
-        <v>199.648311534001</v>
+        <v>162.84171178847</v>
       </c>
       <c r="H16" t="n">
+        <v>136.441631126152</v>
+      </c>
+      <c r="I16" t="n">
+        <v>191.187003850676</v>
+      </c>
+      <c r="J16" t="n">
+        <v>16757.5482834122</v>
+      </c>
+      <c r="K16" t="n">
+        <v>16693.8082289971</v>
+      </c>
+      <c r="L16" t="n">
+        <v>14209.009246409</v>
+      </c>
+      <c r="M16" t="n">
+        <v>19356.5501702144</v>
+      </c>
+      <c r="N16" t="n">
+        <v>976.339054882854</v>
+      </c>
+      <c r="O16" t="n">
         <v>6477.22348854156</v>
       </c>
-      <c r="I16" t="n">
+      <c r="P16" t="n">
         <v>12.1408452842106</v>
       </c>
-      <c r="J16" t="n">
+      <c r="Q16" t="n">
         <v>6.77422709177817</v>
       </c>
-      <c r="K16" t="n">
-        <v>4.57849783821997</v>
-      </c>
-      <c r="L16" t="n">
-        <v>10.0036559722531</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="R16" t="n">
+        <v>6.71928360840837</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.51670400950693</v>
+      </c>
+      <c r="T16" t="n">
+        <v>10.3523288497276</v>
+      </c>
+      <c r="U16" t="n">
+        <v>693.839610112798</v>
+      </c>
+      <c r="V16" t="n">
+        <v>685.697201184405</v>
+      </c>
+      <c r="W16" t="n">
+        <v>466.817551515735</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1059.47865857228</v>
+      </c>
+      <c r="Y16" t="n">
         <v>116.15967753879</v>
       </c>
     </row>
@@ -1101,39 +1700,75 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" t="n">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" t="n">
         <v>0.00115266580349471</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>3.62093598924897</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>25.2345613757424</v>
       </c>
-      <c r="F17" t="n">
-        <v>20.2424250350121</v>
-      </c>
       <c r="G17" t="n">
-        <v>31.044914631816</v>
+        <v>25.3574325292939</v>
       </c>
       <c r="H17" t="n">
+        <v>21.4828048542018</v>
+      </c>
+      <c r="I17" t="n">
+        <v>29.5893084744238</v>
+      </c>
+      <c r="J17" t="n">
+        <v>13416.8603686412</v>
+      </c>
+      <c r="K17" t="n">
+        <v>13484.5529332859</v>
+      </c>
+      <c r="L17" t="n">
+        <v>11558.3563637307</v>
+      </c>
+      <c r="M17" t="n">
+        <v>15417.8381146623</v>
+      </c>
+      <c r="N17" t="n">
+        <v>188.080971869711</v>
+      </c>
+      <c r="O17" t="n">
         <v>6477.22348854156</v>
       </c>
-      <c r="I17" t="n">
+      <c r="P17" t="n">
         <v>15.7071764801393</v>
       </c>
-      <c r="J17" t="n">
+      <c r="Q17" t="n">
         <v>1.68831371385913</v>
       </c>
-      <c r="K17" t="n">
-        <v>1.15869035401604</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2.32630841970805</v>
-      </c>
-      <c r="M17" t="n">
+      <c r="R17" t="n">
+        <v>1.67526593050498</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.080838328349</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.4613234850469</v>
+      </c>
+      <c r="U17" t="n">
+        <v>897.652589241551</v>
+      </c>
+      <c r="V17" t="n">
+        <v>883.775914600129</v>
+      </c>
+      <c r="W17" t="n">
+        <v>581.95257853229</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1310.61785977322</v>
+      </c>
+      <c r="Y17" t="n">
         <v>116.15967753879</v>
       </c>
     </row>
@@ -1142,39 +1777,75 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" t="n">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" t="n">
         <v>0.837486080485109</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>4304.26933910682</v>
       </c>
-      <c r="F18" t="n">
-        <v>4476.50640000144</v>
-      </c>
       <c r="G18" t="n">
-        <v>4127.20635701954</v>
+        <v>4305.1782599323</v>
       </c>
       <c r="H18" t="n">
+        <v>4225.27477879481</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4382.9962285397</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3280.42398755431</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3281.83388848934</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3219.2988645654</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3341.62453335002</v>
+      </c>
+      <c r="N18" t="n">
+        <v>131210.762859829</v>
+      </c>
+      <c r="O18" t="n">
         <v>6219.26831528624</v>
       </c>
-      <c r="I18" t="n">
+      <c r="P18" t="n">
         <v>1</v>
       </c>
-      <c r="J18" t="n">
+      <c r="Q18" t="n">
         <v>56.4517500592786</v>
       </c>
-      <c r="K18" t="n">
-        <v>68.2104376604532</v>
-      </c>
-      <c r="L18" t="n">
-        <v>44.196846642255</v>
-      </c>
-      <c r="M18" t="n">
+      <c r="R18" t="n">
+        <v>56.0397816989548</v>
+      </c>
+      <c r="S18" t="n">
+        <v>49.0226229540244</v>
+      </c>
+      <c r="T18" t="n">
+        <v>62.5354940869211</v>
+      </c>
+      <c r="U18" t="n">
+        <v>43.0237191133364</v>
+      </c>
+      <c r="V18" t="n">
+        <v>42.7260847595514</v>
+      </c>
+      <c r="W18" t="n">
+        <v>37.3624124464848</v>
+      </c>
+      <c r="X18" t="n">
+        <v>47.6476996859891</v>
+      </c>
+      <c r="Y18" t="n">
         <v>116.510679947157</v>
       </c>
     </row>
@@ -1183,39 +1854,75 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" t="n">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" t="n">
         <v>0.00796272428842487</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>1.73620391549785</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>71.0532997566658</v>
       </c>
-      <c r="F19" t="n">
-        <v>65.7833097909221</v>
-      </c>
       <c r="G19" t="n">
-        <v>75.3155208949747</v>
+        <v>70.8270752269238</v>
       </c>
       <c r="H19" t="n">
+        <v>65.1857247293961</v>
+      </c>
+      <c r="I19" t="n">
+        <v>76.9641499103866</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5695.48497168488</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5681.36060956946</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5215.50727932483</v>
+      </c>
+      <c r="M19" t="n">
+        <v>6124.0297492487</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1247.53730560097</v>
+      </c>
+      <c r="O19" t="n">
         <v>6219.26831528624</v>
       </c>
-      <c r="I19" t="n">
+      <c r="P19" t="n">
         <v>3.87720798284478</v>
       </c>
-      <c r="J19" t="n">
+      <c r="Q19" t="n">
         <v>2.08104077247827</v>
       </c>
-      <c r="K19" t="n">
-        <v>1.84518861594824</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2.19134518749484</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="R19" t="n">
+        <v>2.04492911970734</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.51336973977609</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.73163016398175</v>
+      </c>
+      <c r="U19" t="n">
+        <v>166.8119071979</v>
+      </c>
+      <c r="V19" t="n">
+        <v>164.145501250878</v>
+      </c>
+      <c r="W19" t="n">
+        <v>120.772941694977</v>
+      </c>
+      <c r="X19" t="n">
+        <v>218.696695360799</v>
+      </c>
+      <c r="Y19" t="n">
         <v>116.510679947157</v>
       </c>
     </row>
@@ -1224,39 +1931,75 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" t="n">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" t="n">
         <v>0.0933793700035783</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>1.52453466418204</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>731.661301207884</v>
       </c>
-      <c r="F20" t="n">
-        <v>723.758241362174</v>
-      </c>
       <c r="G20" t="n">
-        <v>734.532303040044</v>
+        <v>730.992803631789</v>
       </c>
       <c r="H20" t="n">
+        <v>703.926432393253</v>
+      </c>
+      <c r="I20" t="n">
+        <v>758.337819868456</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5001.12008224082</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4997.94594442734</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4807.42839691991</v>
+      </c>
+      <c r="M20" t="n">
+        <v>5181.34027434444</v>
+      </c>
+      <c r="N20" t="n">
+        <v>14629.9486750187</v>
+      </c>
+      <c r="O20" t="n">
         <v>6219.26831528624</v>
       </c>
-      <c r="I20" t="n">
+      <c r="P20" t="n">
         <v>2.54503453199424</v>
       </c>
-      <c r="J20" t="n">
+      <c r="Q20" t="n">
         <v>16.0193330783995</v>
       </c>
-      <c r="K20" t="n">
-        <v>16.1097904527934</v>
-      </c>
-      <c r="L20" t="n">
-        <v>14.9015969813124</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="R20" t="n">
+        <v>15.8245866132313</v>
+      </c>
+      <c r="S20" t="n">
+        <v>13.4989640118083</v>
+      </c>
+      <c r="T20" t="n">
+        <v>18.4405273477426</v>
+      </c>
+      <c r="U20" t="n">
+        <v>109.496850838262</v>
+      </c>
+      <c r="V20" t="n">
+        <v>108.193690483464</v>
+      </c>
+      <c r="W20" t="n">
+        <v>92.0832061840623</v>
+      </c>
+      <c r="X20" t="n">
+        <v>126.206008093708</v>
+      </c>
+      <c r="Y20" t="n">
         <v>116.510679947157</v>
       </c>
     </row>
@@ -1265,39 +2008,75 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
+        <v>35</v>
+      </c>
+      <c r="C21" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" t="n">
         <v>0.0314915074692897</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>2.89604955563333</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>468.728414373987</v>
       </c>
-      <c r="F21" t="n">
-        <v>402.460735163663</v>
-      </c>
       <c r="G21" t="n">
-        <v>543.757926879779</v>
+        <v>468.330396104358</v>
       </c>
       <c r="H21" t="n">
+        <v>401.882323736649</v>
+      </c>
+      <c r="I21" t="n">
+        <v>543.333823421521</v>
+      </c>
+      <c r="J21" t="n">
+        <v>9500.27043144559</v>
+      </c>
+      <c r="K21" t="n">
+        <v>9515.77129089114</v>
+      </c>
+      <c r="L21" t="n">
+        <v>8134.9531497939</v>
+      </c>
+      <c r="M21" t="n">
+        <v>10957.1153838036</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4933.84286012019</v>
+      </c>
+      <c r="O21" t="n">
         <v>6219.26831528624</v>
       </c>
-      <c r="I21" t="n">
+      <c r="P21" t="n">
         <v>7.90435131698919</v>
       </c>
-      <c r="J21" t="n">
+      <c r="Q21" t="n">
         <v>16.7787459190091</v>
       </c>
-      <c r="K21" t="n">
-        <v>10.7776382456245</v>
-      </c>
-      <c r="L21" t="n">
-        <v>23.5837473720289</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="R21" t="n">
+        <v>16.8566150056653</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10.0079342230628</v>
+      </c>
+      <c r="T21" t="n">
+        <v>26.5096272126247</v>
+      </c>
+      <c r="U21" t="n">
+        <v>340.074590835274</v>
+      </c>
+      <c r="V21" t="n">
+        <v>341.259222580721</v>
+      </c>
+      <c r="W21" t="n">
+        <v>203.908378154924</v>
+      </c>
+      <c r="X21" t="n">
+        <v>528.035359751287</v>
+      </c>
+      <c r="Y21" t="n">
         <v>116.510679947157</v>
       </c>
     </row>
@@ -1306,39 +2085,75 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" t="n">
+        <v>35</v>
+      </c>
+      <c r="C22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" t="n">
         <v>0.00116567943450536</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>2.06769736454035</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>12.3876221687724</v>
       </c>
-      <c r="F22" t="n">
-        <v>11.8869624022894</v>
-      </c>
       <c r="G22" t="n">
-        <v>12.8124561260681</v>
+        <v>12.3565070544279</v>
       </c>
       <c r="H22" t="n">
+        <v>11.6716790215399</v>
+      </c>
+      <c r="I22" t="n">
+        <v>13.1591286126501</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6782.92403364099</v>
+      </c>
+      <c r="K22" t="n">
+        <v>6770.05175958573</v>
+      </c>
+      <c r="L22" t="n">
+        <v>6436.17656099849</v>
+      </c>
+      <c r="M22" t="n">
+        <v>7158.39729149732</v>
+      </c>
+      <c r="N22" t="n">
+        <v>182.629528317493</v>
+      </c>
+      <c r="O22" t="n">
         <v>6219.26831528624</v>
       </c>
-      <c r="I22" t="n">
+      <c r="P22" t="n">
         <v>5.03462423827642</v>
       </c>
-      <c r="J22" t="n">
+      <c r="Q22" t="n">
         <v>0.395590641834083</v>
       </c>
-      <c r="K22" t="n">
-        <v>0.386511391365004</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.380907535309701</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="R22" t="n">
+        <v>0.388609835037175</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.326428162855232</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.470366714751712</v>
+      </c>
+      <c r="U22" t="n">
+        <v>216.6082590688</v>
+      </c>
+      <c r="V22" t="n">
+        <v>212.416586575614</v>
+      </c>
+      <c r="W22" t="n">
+        <v>178.980909290241</v>
+      </c>
+      <c r="X22" t="n">
+        <v>256.467530966725</v>
+      </c>
+      <c r="Y22" t="n">
         <v>116.510679947157</v>
       </c>
     </row>
@@ -1347,39 +2162,75 @@
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" t="n">
+        <v>35</v>
+      </c>
+      <c r="C23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" t="n">
         <v>0.000520094954202415</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>3.63699661366556</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>9.7218155937674</v>
       </c>
-      <c r="F23" t="n">
-        <v>6.9995829097176</v>
-      </c>
       <c r="G23" t="n">
-        <v>13.2484146598995</v>
+        <v>9.6355622056399</v>
       </c>
       <c r="H23" t="n">
+        <v>6.91738896011082</v>
+      </c>
+      <c r="I23" t="n">
+        <v>13.4426307578758</v>
+      </c>
+      <c r="J23" t="n">
+        <v>11930.8909341223</v>
+      </c>
+      <c r="K23" t="n">
+        <v>11843.4999580788</v>
+      </c>
+      <c r="L23" t="n">
+        <v>8531.6061966321</v>
+      </c>
+      <c r="M23" t="n">
+        <v>16454.936669956</v>
+      </c>
+      <c r="N23" t="n">
+        <v>81.4844058792209</v>
+      </c>
+      <c r="O23" t="n">
         <v>6219.26831528624</v>
       </c>
-      <c r="I23" t="n">
+      <c r="P23" t="n">
         <v>10.1868679468459</v>
       </c>
-      <c r="J23" t="n">
+      <c r="Q23" t="n">
         <v>0.357127364893465</v>
       </c>
-      <c r="K23" t="n">
-        <v>0.16202486781153</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.730001289809793</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="R23" t="n">
+        <v>0.35563081971165</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.141419799905982</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.883547637569305</v>
+      </c>
+      <c r="U23" t="n">
+        <v>438.276945189748</v>
+      </c>
+      <c r="V23" t="n">
+        <v>435.988833145395</v>
+      </c>
+      <c r="W23" t="n">
+        <v>173.286956853394</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1074.54727686531</v>
+      </c>
+      <c r="Y23" t="n">
         <v>116.510679947157</v>
       </c>
     </row>
@@ -1388,39 +2239,75 @@
         <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>19</v>
-      </c>
-      <c r="C24" t="n">
+        <v>35</v>
+      </c>
+      <c r="C24" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" t="n">
         <v>0.0216830050339063</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>4.52251927826614</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>503.989791039603</v>
       </c>
-      <c r="F24" t="n">
-        <v>431.244465759581</v>
-      </c>
       <c r="G24" t="n">
-        <v>577.131936123187</v>
+        <v>501.301865584908</v>
       </c>
       <c r="H24" t="n">
+        <v>431.019576450913</v>
+      </c>
+      <c r="I24" t="n">
+        <v>580.34051831527</v>
+      </c>
+      <c r="J24" t="n">
+        <v>14835.780724601</v>
+      </c>
+      <c r="K24" t="n">
+        <v>14774.058777044</v>
+      </c>
+      <c r="L24" t="n">
+        <v>12696.2828834883</v>
+      </c>
+      <c r="M24" t="n">
+        <v>17036.7839985755</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3397.1234840636</v>
+      </c>
+      <c r="O24" t="n">
         <v>6219.26831528624</v>
       </c>
-      <c r="I24" t="n">
+      <c r="P24" t="n">
         <v>12.1408452842106</v>
       </c>
-      <c r="J24" t="n">
+      <c r="Q24" t="n">
         <v>17.7446814708858</v>
       </c>
-      <c r="K24" t="n">
-        <v>13.7450373537562</v>
-      </c>
-      <c r="L24" t="n">
-        <v>22.6036421553109</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="R24" t="n">
+        <v>17.5182895493717</v>
+      </c>
+      <c r="S24" t="n">
+        <v>12.3008534747066</v>
+      </c>
+      <c r="T24" t="n">
+        <v>25.7290863335847</v>
+      </c>
+      <c r="U24" t="n">
+        <v>522.344317306354</v>
+      </c>
+      <c r="V24" t="n">
+        <v>516.907319611996</v>
+      </c>
+      <c r="W24" t="n">
+        <v>362.403206900417</v>
+      </c>
+      <c r="X24" t="n">
+        <v>752.009312551229</v>
+      </c>
+      <c r="Y24" t="n">
         <v>116.510679947157</v>
       </c>
     </row>
@@ -1429,39 +2316,75 @@
         <v>20</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" t="n">
+        <v>35</v>
+      </c>
+      <c r="C25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" t="n">
         <v>0.00631153833098439</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>3.62093598924897</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>117.456732038746</v>
       </c>
-      <c r="F25" t="n">
-        <v>100.628617896454</v>
-      </c>
       <c r="G25" t="n">
-        <v>135.263400542752</v>
+        <v>118.31069978434</v>
       </c>
       <c r="H25" t="n">
+        <v>101.373560360006</v>
+      </c>
+      <c r="I25" t="n">
+        <v>135.846667310753</v>
+      </c>
+      <c r="J25" t="n">
+        <v>11878.205276531</v>
+      </c>
+      <c r="K25" t="n">
+        <v>11938.3145246558</v>
+      </c>
+      <c r="L25" t="n">
+        <v>10247.9484155651</v>
+      </c>
+      <c r="M25" t="n">
+        <v>13625.9676691039</v>
+      </c>
+      <c r="N25" t="n">
+        <v>988.84241604089</v>
+      </c>
+      <c r="O25" t="n">
         <v>6219.26831528624</v>
       </c>
-      <c r="I25" t="n">
+      <c r="P25" t="n">
         <v>15.7071764801393</v>
       </c>
-      <c r="J25" t="n">
+      <c r="Q25" t="n">
         <v>6.68241064037778</v>
       </c>
-      <c r="K25" t="n">
-        <v>5.27405135940455</v>
-      </c>
-      <c r="L25" t="n">
-        <v>7.92259278363508</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="R25" t="n">
+        <v>6.54156889164085</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.50542762254854</v>
+      </c>
+      <c r="T25" t="n">
+        <v>9.54441212077915</v>
+      </c>
+      <c r="U25" t="n">
+        <v>675.781148945117</v>
+      </c>
+      <c r="V25" t="n">
+        <v>664.753955117304</v>
+      </c>
+      <c r="W25" t="n">
+        <v>452.827842302218</v>
+      </c>
+      <c r="X25" t="n">
+        <v>964.25282495181</v>
+      </c>
+      <c r="Y25" t="n">
         <v>116.510679947157</v>
       </c>
     </row>
@@ -1470,39 +2393,75 @@
         <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" t="n">
+        <v>36</v>
+      </c>
+      <c r="C26" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" t="n">
         <v>0.713017659610737</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>1</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>2961.75707635757</v>
       </c>
-      <c r="F26" t="n">
-        <v>3119.26244736399</v>
-      </c>
       <c r="G26" t="n">
-        <v>2806.44155150266</v>
+        <v>2962.22794209069</v>
       </c>
       <c r="H26" t="n">
+        <v>2894.67026447566</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3032.67634151544</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2994.32581939306</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2995.5812489335</v>
+      </c>
+      <c r="L26" t="n">
+        <v>2927.56629389881</v>
+      </c>
+      <c r="M26" t="n">
+        <v>3065.74240969408</v>
+      </c>
+      <c r="N26" t="n">
+        <v>98912.3179974418</v>
+      </c>
+      <c r="O26" t="n">
         <v>5506.77743475503</v>
       </c>
-      <c r="I26" t="n">
+      <c r="P26" t="n">
         <v>1</v>
       </c>
-      <c r="J26" t="n">
+      <c r="Q26" t="n">
         <v>39.4368165998026</v>
       </c>
-      <c r="K26" t="n">
-        <v>49.6976833109703</v>
-      </c>
-      <c r="L26" t="n">
-        <v>29.8254147841575</v>
-      </c>
-      <c r="M26" t="n">
+      <c r="R26" t="n">
+        <v>39.2551401833984</v>
+      </c>
+      <c r="S26" t="n">
+        <v>33.8480174109546</v>
+      </c>
+      <c r="T26" t="n">
+        <v>44.15239812343</v>
+      </c>
+      <c r="U26" t="n">
+        <v>39.87048064208</v>
+      </c>
+      <c r="V26" t="n">
+        <v>39.6607925577677</v>
+      </c>
+      <c r="W26" t="n">
+        <v>34.2372110402686</v>
+      </c>
+      <c r="X26" t="n">
+        <v>44.6337694194615</v>
+      </c>
+      <c r="Y26" t="n">
         <v>119.251791288822</v>
       </c>
     </row>
@@ -1511,39 +2470,75 @@
         <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" t="n">
+        <v>36</v>
+      </c>
+      <c r="C27" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" t="n">
         <v>0.016515715062824</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>1.73620391549785</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>119.109735803819</v>
       </c>
-      <c r="F27" t="n">
-        <v>111.754354969124</v>
-      </c>
       <c r="G27" t="n">
-        <v>124.667750880493</v>
+        <v>118.721703039483</v>
       </c>
       <c r="H27" t="n">
+        <v>109.373974388525</v>
+      </c>
+      <c r="I27" t="n">
+        <v>128.814035616333</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5198.76021190655</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5188.0986515157</v>
+      </c>
+      <c r="L27" t="n">
+        <v>4775.69743213159</v>
+      </c>
+      <c r="M27" t="n">
+        <v>5582.30928957438</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2291.11809256033</v>
+      </c>
+      <c r="O27" t="n">
         <v>5506.77743475503</v>
       </c>
-      <c r="I27" t="n">
+      <c r="P27" t="n">
         <v>3.87720798284478</v>
       </c>
-      <c r="J27" t="n">
+      <c r="Q27" t="n">
         <v>3.54175115559586</v>
       </c>
-      <c r="K27" t="n">
-        <v>3.27764643151917</v>
-      </c>
-      <c r="L27" t="n">
-        <v>3.5997788790524</v>
-      </c>
-      <c r="M27" t="n">
+      <c r="R27" t="n">
+        <v>3.47797275818646</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.57814146732706</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4.59984868162429</v>
+      </c>
+      <c r="U27" t="n">
+        <v>154.586145825331</v>
+      </c>
+      <c r="V27" t="n">
+        <v>151.619241781883</v>
+      </c>
+      <c r="W27" t="n">
+        <v>112.880499054566</v>
+      </c>
+      <c r="X27" t="n">
+        <v>199.510520289876</v>
+      </c>
+      <c r="Y27" t="n">
         <v>119.251791288822</v>
       </c>
     </row>
@@ -1552,39 +2547,75 @@
         <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" t="n">
+        <v>36</v>
+      </c>
+      <c r="C28" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" t="n">
         <v>0.184083037364504</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>1.52453466418204</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>1165.73604061667</v>
       </c>
-      <c r="F28" t="n">
-        <v>1173.5865550381</v>
-      </c>
       <c r="G28" t="n">
-        <v>1151.06453112478</v>
+        <v>1164.88147258566</v>
       </c>
       <c r="H28" t="n">
+        <v>1123.38456759416</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1204.72894428222</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4564.95350752002</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4561.00327698949</v>
+      </c>
+      <c r="L28" t="n">
+        <v>4398.7076825936</v>
+      </c>
+      <c r="M28" t="n">
+        <v>4720.58713216878</v>
+      </c>
+      <c r="N28" t="n">
+        <v>25536.6465112144</v>
+      </c>
+      <c r="O28" t="n">
         <v>5506.77743475503</v>
       </c>
-      <c r="I28" t="n">
+      <c r="P28" t="n">
         <v>2.54503453199424</v>
       </c>
-      <c r="J28" t="n">
+      <c r="Q28" t="n">
         <v>25.9124821167902</v>
       </c>
-      <c r="K28" t="n">
-        <v>27.3139239534074</v>
-      </c>
-      <c r="L28" t="n">
-        <v>23.1748523190222</v>
-      </c>
-      <c r="M28" t="n">
+      <c r="R28" t="n">
+        <v>25.6139293606665</v>
+      </c>
+      <c r="S28" t="n">
+        <v>21.8872186957746</v>
+      </c>
+      <c r="T28" t="n">
+        <v>29.7556252251555</v>
+      </c>
+      <c r="U28" t="n">
+        <v>101.471750041302</v>
+      </c>
+      <c r="V28" t="n">
+        <v>100.251328509123</v>
+      </c>
+      <c r="W28" t="n">
+        <v>85.6851253119309</v>
+      </c>
+      <c r="X28" t="n">
+        <v>116.507844777141</v>
+      </c>
+      <c r="Y28" t="n">
         <v>119.251791288822</v>
       </c>
     </row>
@@ -1593,39 +2624,75 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
+        <v>36</v>
+      </c>
+      <c r="C29" t="s">
+        <v>29</v>
+      </c>
+      <c r="D29" t="n">
         <v>0.0364306543257774</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>2.89604955563333</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>438.250185950471</v>
       </c>
-      <c r="F29" t="n">
-        <v>381.337987103085</v>
-      </c>
       <c r="G29" t="n">
-        <v>502.010798964958</v>
+        <v>438.43271108301</v>
       </c>
       <c r="H29" t="n">
+        <v>376.702877840622</v>
+      </c>
+      <c r="I29" t="n">
+        <v>507.579971573045</v>
+      </c>
+      <c r="J29" t="n">
+        <v>8671.71595867469</v>
+      </c>
+      <c r="K29" t="n">
+        <v>8681.27944057598</v>
+      </c>
+      <c r="L29" t="n">
+        <v>7432.25344169741</v>
+      </c>
+      <c r="M29" t="n">
+        <v>9996.63000379073</v>
+      </c>
+      <c r="N29" t="n">
+        <v>5053.78852396647</v>
+      </c>
+      <c r="O29" t="n">
         <v>5506.77743475503</v>
       </c>
-      <c r="I29" t="n">
+      <c r="P29" t="n">
         <v>7.90435131698919</v>
       </c>
-      <c r="J29" t="n">
+      <c r="Q29" t="n">
         <v>15.927028995819</v>
       </c>
-      <c r="K29" t="n">
-        <v>10.6778239711062</v>
-      </c>
-      <c r="L29" t="n">
-        <v>21.6080542837227</v>
-      </c>
-      <c r="M29" t="n">
+      <c r="R29" t="n">
+        <v>15.9555127891446</v>
+      </c>
+      <c r="S29" t="n">
+        <v>9.61484116143891</v>
+      </c>
+      <c r="T29" t="n">
+        <v>25.3738878158625</v>
+      </c>
+      <c r="U29" t="n">
+        <v>315.150286172217</v>
+      </c>
+      <c r="V29" t="n">
+        <v>316.288890660919</v>
+      </c>
+      <c r="W29" t="n">
+        <v>189.727982435953</v>
+      </c>
+      <c r="X29" t="n">
+        <v>500.562006220594</v>
+      </c>
+      <c r="Y29" t="n">
         <v>119.251791288822</v>
       </c>
     </row>
@@ -1634,39 +2701,75 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" t="n">
+        <v>36</v>
+      </c>
+      <c r="C30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D30" t="n">
         <v>0.00516043616960476</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>2.06769736454035</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>44.3223249219607</v>
       </c>
-      <c r="F30" t="n">
-        <v>43.1013821955664</v>
-      </c>
       <c r="G30" t="n">
-        <v>45.2661548217112</v>
+        <v>44.2307145183891</v>
       </c>
       <c r="H30" t="n">
+        <v>41.7827069320138</v>
+      </c>
+      <c r="I30" t="n">
+        <v>46.9611052492658</v>
+      </c>
+      <c r="J30" t="n">
+        <v>6191.35960533415</v>
+      </c>
+      <c r="K30" t="n">
+        <v>6174.90349722147</v>
+      </c>
+      <c r="L30" t="n">
+        <v>5876.26267055564</v>
+      </c>
+      <c r="M30" t="n">
+        <v>6544.04875139655</v>
+      </c>
+      <c r="N30" t="n">
+        <v>715.873858849596</v>
+      </c>
+      <c r="O30" t="n">
         <v>5506.77743475503</v>
       </c>
-      <c r="I30" t="n">
+      <c r="P30" t="n">
         <v>5.03462423827642</v>
       </c>
-      <c r="J30" t="n">
+      <c r="Q30" t="n">
         <v>1.43699427296915</v>
       </c>
-      <c r="K30" t="n">
-        <v>1.46539669486731</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.33553774687982</v>
-      </c>
-      <c r="M30" t="n">
+      <c r="R30" t="n">
+        <v>1.41396044197836</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.18374769575253</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.71870084980845</v>
+      </c>
+      <c r="U30" t="n">
+        <v>200.732888232347</v>
+      </c>
+      <c r="V30" t="n">
+        <v>197.383112833192</v>
+      </c>
+      <c r="W30" t="n">
+        <v>166.36815046856</v>
+      </c>
+      <c r="X30" t="n">
+        <v>238.274387984315</v>
+      </c>
+      <c r="Y30" t="n">
         <v>119.251791288822</v>
       </c>
     </row>
@@ -1675,39 +2778,75 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>18</v>
-      </c>
-      <c r="C31" t="n">
+        <v>36</v>
+      </c>
+      <c r="C31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" t="n">
         <v>0.00147551430839683</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>3.63699661366556</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>22.291303783304</v>
       </c>
-      <c r="F31" t="n">
-        <v>16.2646970877761</v>
-      </c>
       <c r="G31" t="n">
-        <v>29.9956746714777</v>
+        <v>22.0944983244889</v>
       </c>
       <c r="H31" t="n">
+        <v>15.8625447697409</v>
+      </c>
+      <c r="I31" t="n">
+        <v>30.884091727978</v>
+      </c>
+      <c r="J31" t="n">
+        <v>10890.3528653439</v>
+      </c>
+      <c r="K31" t="n">
+        <v>10819.9045556725</v>
+      </c>
+      <c r="L31" t="n">
+        <v>7804.33700365094</v>
+      </c>
+      <c r="M31" t="n">
+        <v>15032.9640284889</v>
+      </c>
+      <c r="N31" t="n">
+        <v>204.688535430666</v>
+      </c>
+      <c r="O31" t="n">
         <v>5506.77743475503</v>
       </c>
-      <c r="I31" t="n">
+      <c r="P31" t="n">
         <v>10.1868679468459</v>
       </c>
-      <c r="J31" t="n">
+      <c r="Q31" t="n">
         <v>0.831353378697948</v>
       </c>
-      <c r="K31" t="n">
-        <v>0.393666169343573</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.64026394738032</v>
-      </c>
-      <c r="M31" t="n">
+      <c r="R31" t="n">
+        <v>0.828620504931106</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.332369051213169</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.04489686994992</v>
+      </c>
+      <c r="U31" t="n">
+        <v>406.155321278144</v>
+      </c>
+      <c r="V31" t="n">
+        <v>404.448671997873</v>
+      </c>
+      <c r="W31" t="n">
+        <v>157.987248699156</v>
+      </c>
+      <c r="X31" t="n">
+        <v>996.341470268298</v>
+      </c>
+      <c r="Y31" t="n">
         <v>119.251791288822</v>
       </c>
     </row>
@@ -1716,39 +2855,75 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>19</v>
-      </c>
-      <c r="C32" t="n">
+        <v>36</v>
+      </c>
+      <c r="C32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" t="n">
         <v>0.027714108972301</v>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>4.52251927826614</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>520.631565506778</v>
       </c>
-      <c r="F32" t="n">
-        <v>457.46965583187</v>
-      </c>
       <c r="G32" t="n">
-        <v>580.789117663571</v>
+        <v>517.109638769265</v>
       </c>
       <c r="H32" t="n">
+        <v>447.515634459631</v>
+      </c>
+      <c r="I32" t="n">
+        <v>595.193180087089</v>
+      </c>
+      <c r="J32" t="n">
+        <v>13541.8962436152</v>
+      </c>
+      <c r="K32" t="n">
+        <v>13477.8328322417</v>
+      </c>
+      <c r="L32" t="n">
+        <v>11599.1989484504</v>
+      </c>
+      <c r="M32" t="n">
+        <v>15494.1294486408</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3844.59868943575</v>
+      </c>
+      <c r="O32" t="n">
         <v>5506.77743475503</v>
       </c>
-      <c r="I32" t="n">
+      <c r="P32" t="n">
         <v>12.1408452842106</v>
       </c>
-      <c r="J32" t="n">
+      <c r="Q32" t="n">
         <v>18.610215813854</v>
       </c>
-      <c r="K32" t="n">
-        <v>15.2460480160785</v>
-      </c>
-      <c r="L32" t="n">
-        <v>22.5744499076053</v>
-      </c>
-      <c r="M32" t="n">
+      <c r="R32" t="n">
+        <v>18.4017823169194</v>
+      </c>
+      <c r="S32" t="n">
+        <v>12.8835555863581</v>
+      </c>
+      <c r="T32" t="n">
+        <v>26.5038818815804</v>
+      </c>
+      <c r="U32" t="n">
+        <v>484.061336882609</v>
+      </c>
+      <c r="V32" t="n">
+        <v>479.489690569739</v>
+      </c>
+      <c r="W32" t="n">
+        <v>335.141007940569</v>
+      </c>
+      <c r="X32" t="n">
+        <v>691.106955210844</v>
+      </c>
+      <c r="Y32" t="n">
         <v>119.251791288822</v>
       </c>
     </row>
@@ -1757,39 +2932,75 @@
         <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>20</v>
-      </c>
-      <c r="C33" t="n">
+        <v>36</v>
+      </c>
+      <c r="C33" t="s">
+        <v>33</v>
+      </c>
+      <c r="D33" t="n">
         <v>0.0156028741858547</v>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
         <v>3.62093598924897</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>234.679201814457</v>
       </c>
-      <c r="F33" t="n">
-        <v>204.000355165519</v>
-      </c>
       <c r="G33" t="n">
-        <v>266.541855125383</v>
+        <v>236.180357431667</v>
       </c>
       <c r="H33" t="n">
+        <v>203.016241305337</v>
+      </c>
+      <c r="I33" t="n">
+        <v>270.327762941152</v>
+      </c>
+      <c r="J33" t="n">
+        <v>10842.2621229778</v>
+      </c>
+      <c r="K33" t="n">
+        <v>10890.3248926071</v>
+      </c>
+      <c r="L33" t="n">
+        <v>9383.71604565797</v>
+      </c>
+      <c r="M33" t="n">
+        <v>12389.9096312715</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2164.48559491204</v>
+      </c>
+      <c r="O33" t="n">
         <v>5506.77743475503</v>
       </c>
-      <c r="I33" t="n">
+      <c r="P33" t="n">
         <v>15.7071764801393</v>
       </c>
-      <c r="J33" t="n">
+      <c r="Q33" t="n">
         <v>13.5551489552934</v>
       </c>
-      <c r="K33" t="n">
-        <v>11.1796027415297</v>
-      </c>
-      <c r="L33" t="n">
-        <v>15.493439421002</v>
-      </c>
-      <c r="M33" t="n">
+      <c r="R33" t="n">
+        <v>13.2874734357991</v>
+      </c>
+      <c r="S33" t="n">
+        <v>9.38747714804509</v>
+      </c>
+      <c r="T33" t="n">
+        <v>18.9502501598279</v>
+      </c>
+      <c r="U33" t="n">
+        <v>626.252675793128</v>
+      </c>
+      <c r="V33" t="n">
+        <v>615.264827151045</v>
+      </c>
+      <c r="W33" t="n">
+        <v>428.136309524608</v>
+      </c>
+      <c r="X33" t="n">
+        <v>871.985237442174</v>
+      </c>
+      <c r="Y33" t="n">
         <v>119.251791288822</v>
       </c>
     </row>
@@ -1798,39 +3009,75 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
-      </c>
-      <c r="C34" t="n">
+        <v>37</v>
+      </c>
+      <c r="C34" t="s">
+        <v>26</v>
+      </c>
+      <c r="D34" t="n">
         <v>0.580783095220194</v>
       </c>
-      <c r="D34" t="n">
+      <c r="E34" t="n">
         <v>1</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>1661.51389189512</v>
       </c>
-      <c r="F34" t="n">
-        <v>1761.89879420553</v>
-      </c>
       <c r="G34" t="n">
-        <v>1565.93728481275</v>
+        <v>1661.64838773179</v>
       </c>
       <c r="H34" t="n">
+        <v>1615.68742131413</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1707.40300550194</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2744.52981078097</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2744.38852218085</v>
+      </c>
+      <c r="L34" t="n">
+        <v>2671.04645172566</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2820.10190523872</v>
+      </c>
+      <c r="N34" t="n">
+        <v>60539.1089347406</v>
+      </c>
+      <c r="O34" t="n">
         <v>4137.79993345024</v>
       </c>
-      <c r="I34" t="n">
+      <c r="P34" t="n">
         <v>1</v>
       </c>
-      <c r="J34" t="n">
+      <c r="Q34" t="n">
         <v>21.6106965394249</v>
       </c>
-      <c r="K34" t="n">
-        <v>27.7876913386583</v>
-      </c>
-      <c r="L34" t="n">
-        <v>16.2557666265266</v>
-      </c>
-      <c r="M34" t="n">
+      <c r="R34" t="n">
+        <v>21.5643238231657</v>
+      </c>
+      <c r="S34" t="n">
+        <v>18.2679314346303</v>
+      </c>
+      <c r="T34" t="n">
+        <v>25.0353072022468</v>
+      </c>
+      <c r="U34" t="n">
+        <v>35.697083950675</v>
+      </c>
+      <c r="V34" t="n">
+        <v>35.6198199411902</v>
+      </c>
+      <c r="W34" t="n">
+        <v>30.1824173678484</v>
+      </c>
+      <c r="X34" t="n">
+        <v>41.3192324346767</v>
+      </c>
+      <c r="Y34" t="n">
         <v>100.906190368132</v>
       </c>
     </row>
@@ -1839,39 +3086,75 @@
         <v>40</v>
       </c>
       <c r="B35" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" t="n">
+        <v>37</v>
+      </c>
+      <c r="C35" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" t="n">
         <v>0.0195460168961236</v>
       </c>
-      <c r="D35" t="n">
+      <c r="E35" t="n">
         <v>1.73620391549785</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>97.0843016543562</v>
       </c>
-      <c r="F35" t="n">
-        <v>92.4873975060663</v>
-      </c>
       <c r="G35" t="n">
-        <v>100.465492150505</v>
+        <v>96.9197996824014</v>
       </c>
       <c r="H35" t="n">
+        <v>88.6401960494241</v>
+      </c>
+      <c r="I35" t="n">
+        <v>105.107491354856</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4765.0634036785</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4757.6533684726</v>
+      </c>
+      <c r="L35" t="n">
+        <v>4367.66226520522</v>
+      </c>
+      <c r="M35" t="n">
+        <v>5128.40084774616</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2037.41888469752</v>
+      </c>
+      <c r="O35" t="n">
         <v>4137.79993345024</v>
       </c>
-      <c r="I35" t="n">
+      <c r="P35" t="n">
         <v>3.87720798284478</v>
       </c>
-      <c r="J35" t="n">
+      <c r="Q35" t="n">
         <v>2.81988999157875</v>
       </c>
-      <c r="K35" t="n">
-        <v>2.68514341408448</v>
-      </c>
-      <c r="L35" t="n">
-        <v>2.83361743970793</v>
-      </c>
-      <c r="M35" t="n">
+      <c r="R35" t="n">
+        <v>2.76904169988831</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.03508588876233</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3.68410950730295</v>
+      </c>
+      <c r="U35" t="n">
+        <v>138.405018857838</v>
+      </c>
+      <c r="V35" t="n">
+        <v>135.51025449015</v>
+      </c>
+      <c r="W35" t="n">
+        <v>100.382935968874</v>
+      </c>
+      <c r="X35" t="n">
+        <v>180.976095522067</v>
+      </c>
+      <c r="Y35" t="n">
         <v>100.906190368132</v>
       </c>
     </row>
@@ -1880,39 +3163,75 @@
         <v>40</v>
       </c>
       <c r="B36" t="s">
-        <v>15</v>
-      </c>
-      <c r="C36" t="n">
+        <v>37</v>
+      </c>
+      <c r="C36" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" t="n">
         <v>0.287662722623673</v>
       </c>
-      <c r="D36" t="n">
+      <c r="E36" t="n">
         <v>1.52453466418204</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>1254.61622610416</v>
       </c>
-      <c r="F36" t="n">
-        <v>1276.16322254628</v>
-      </c>
       <c r="G36" t="n">
-        <v>1228.50491093671</v>
+        <v>1254.30580799564</v>
       </c>
       <c r="H36" t="n">
+        <v>1211.53312730979</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1296.44893057793</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4184.13083341656</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4184.2919329073</v>
+      </c>
+      <c r="L36" t="n">
+        <v>4041.8098471933</v>
+      </c>
+      <c r="M36" t="n">
+        <v>4324.74956379139</v>
+      </c>
+      <c r="N36" t="n">
+        <v>29985.109836532</v>
+      </c>
+      <c r="O36" t="n">
         <v>4137.79993345024</v>
       </c>
-      <c r="I36" t="n">
+      <c r="P36" t="n">
         <v>2.54503453199424</v>
       </c>
-      <c r="J36" t="n">
+      <c r="Q36" t="n">
         <v>27.2415656439191</v>
       </c>
-      <c r="K36" t="n">
-        <v>29.4010252748034</v>
-      </c>
-      <c r="L36" t="n">
-        <v>24.1599928314541</v>
-      </c>
-      <c r="M36" t="n">
+      <c r="R36" t="n">
+        <v>27.0003238391343</v>
+      </c>
+      <c r="S36" t="n">
+        <v>22.9237991760855</v>
+      </c>
+      <c r="T36" t="n">
+        <v>31.3450665440307</v>
+      </c>
+      <c r="U36" t="n">
+        <v>90.8503113459654</v>
+      </c>
+      <c r="V36" t="n">
+        <v>90.0583478922713</v>
+      </c>
+      <c r="W36" t="n">
+        <v>76.4189638092812</v>
+      </c>
+      <c r="X36" t="n">
+        <v>104.407702725808</v>
+      </c>
+      <c r="Y36" t="n">
         <v>100.906190368132</v>
       </c>
     </row>
@@ -1921,39 +3240,75 @@
         <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
+        <v>37</v>
+      </c>
+      <c r="C37" t="s">
+        <v>29</v>
+      </c>
+      <c r="D37" t="n">
         <v>0.0256406080502322</v>
       </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
         <v>2.89604955563333</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>212.434142899312</v>
       </c>
-      <c r="F37" t="n">
-        <v>187.684597258549</v>
-      </c>
       <c r="G37" t="n">
-        <v>240.589301482819</v>
+        <v>212.461031507917</v>
       </c>
       <c r="H37" t="n">
+        <v>180.178010485525</v>
+      </c>
+      <c r="I37" t="n">
+        <v>246.556271894816</v>
+      </c>
+      <c r="J37" t="n">
+        <v>7948.29433893465</v>
+      </c>
+      <c r="K37" t="n">
+        <v>7954.88509171966</v>
+      </c>
+      <c r="L37" t="n">
+        <v>6772.10779115519</v>
+      </c>
+      <c r="M37" t="n">
+        <v>9215.05325720575</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2672.70100779617</v>
+      </c>
+      <c r="O37" t="n">
         <v>4137.79993345024</v>
       </c>
-      <c r="I37" t="n">
+      <c r="P37" t="n">
         <v>7.90435131698919</v>
       </c>
-      <c r="J37" t="n">
+      <c r="Q37" t="n">
         <v>7.54135443628904</v>
       </c>
-      <c r="K37" t="n">
-        <v>5.20221863340021</v>
-      </c>
-      <c r="L37" t="n">
-        <v>10.1153639806739</v>
-      </c>
-      <c r="M37" t="n">
+      <c r="R37" t="n">
+        <v>7.55600666732368</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4.35828786214613</v>
+      </c>
+      <c r="T37" t="n">
+        <v>12.4214279807206</v>
+      </c>
+      <c r="U37" t="n">
+        <v>282.162292538192</v>
+      </c>
+      <c r="V37" t="n">
+        <v>283.002571428918</v>
+      </c>
+      <c r="W37" t="n">
+        <v>162.599589045628</v>
+      </c>
+      <c r="X37" t="n">
+        <v>463.021779794846</v>
+      </c>
+      <c r="Y37" t="n">
         <v>100.906190368132</v>
       </c>
     </row>
@@ -1962,39 +3317,75 @@
         <v>40</v>
       </c>
       <c r="B38" t="s">
-        <v>17</v>
-      </c>
-      <c r="C38" t="n">
+        <v>37</v>
+      </c>
+      <c r="C38" t="s">
+        <v>30</v>
+      </c>
+      <c r="D38" t="n">
         <v>0.0118921712139969</v>
       </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
         <v>2.06769736454035</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>70.345794214048</v>
       </c>
-      <c r="F38" t="n">
-        <v>69.4581408816609</v>
-      </c>
       <c r="G38" t="n">
-        <v>71.0313797117548</v>
+        <v>70.0772743793073</v>
       </c>
       <c r="H38" t="n">
+        <v>66.4577232557021</v>
+      </c>
+      <c r="I38" t="n">
+        <v>74.7666447681449</v>
+      </c>
+      <c r="J38" t="n">
+        <v>5674.85705665422</v>
+      </c>
+      <c r="K38" t="n">
+        <v>5658.77215456666</v>
+      </c>
+      <c r="L38" t="n">
+        <v>5379.08178933771</v>
+      </c>
+      <c r="M38" t="n">
+        <v>6001.89763015779</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1239.60468980557</v>
+      </c>
+      <c r="O38" t="n">
         <v>4137.79993345024</v>
       </c>
-      <c r="I38" t="n">
+      <c r="P38" t="n">
         <v>5.03462423827642</v>
       </c>
-      <c r="J38" t="n">
+      <c r="Q38" t="n">
         <v>2.22783495373187</v>
       </c>
-      <c r="K38" t="n">
-        <v>2.33762285782219</v>
-      </c>
-      <c r="L38" t="n">
-        <v>2.04708282152738</v>
-      </c>
-      <c r="M38" t="n">
+      <c r="R38" t="n">
+        <v>2.19281933779452</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1.82436821680912</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.67109541942577</v>
+      </c>
+      <c r="U38" t="n">
+        <v>179.721404093857</v>
+      </c>
+      <c r="V38" t="n">
+        <v>176.985847449481</v>
+      </c>
+      <c r="W38" t="n">
+        <v>146.917097339416</v>
+      </c>
+      <c r="X38" t="n">
+        <v>214.31404269309</v>
+      </c>
+      <c r="Y38" t="n">
         <v>100.906190368132</v>
       </c>
     </row>
@@ -2003,39 +3394,75 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>18</v>
-      </c>
-      <c r="C39" t="n">
+        <v>37</v>
+      </c>
+      <c r="C39" t="s">
+        <v>31</v>
+      </c>
+      <c r="D39" t="n">
         <v>0.00218937448048026</v>
       </c>
-      <c r="D39" t="n">
+      <c r="E39" t="n">
         <v>3.63699661366556</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>22.7799600516482</v>
       </c>
-      <c r="F39" t="n">
-        <v>16.8764003870957</v>
-      </c>
       <c r="G39" t="n">
-        <v>30.306596322452</v>
+        <v>22.6664805700374</v>
       </c>
       <c r="H39" t="n">
+        <v>16.2194651535111</v>
+      </c>
+      <c r="I39" t="n">
+        <v>31.3996379311371</v>
+      </c>
+      <c r="J39" t="n">
+        <v>9981.84562791457</v>
+      </c>
+      <c r="K39" t="n">
+        <v>9909.81334501022</v>
+      </c>
+      <c r="L39" t="n">
+        <v>7088.15538872892</v>
+      </c>
+      <c r="M39" t="n">
+        <v>13712.8392053044</v>
+      </c>
+      <c r="N39" t="n">
+        <v>228.213908537548</v>
+      </c>
+      <c r="O39" t="n">
         <v>4137.79993345024</v>
       </c>
-      <c r="I39" t="n">
+      <c r="P39" t="n">
         <v>10.1868679468459</v>
       </c>
-      <c r="J39" t="n">
+      <c r="Q39" t="n">
         <v>0.82988043524045</v>
       </c>
-      <c r="K39" t="n">
-        <v>0.404342335680767</v>
-      </c>
-      <c r="L39" t="n">
-        <v>1.61880623932612</v>
-      </c>
-      <c r="M39" t="n">
+      <c r="R39" t="n">
+        <v>0.822518386643004</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.338531631642506</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.0232979186556</v>
+      </c>
+      <c r="U39" t="n">
+        <v>363.641480292998</v>
+      </c>
+      <c r="V39" t="n">
+        <v>358.909588824031</v>
+      </c>
+      <c r="W39" t="n">
+        <v>149.710622567297</v>
+      </c>
+      <c r="X39" t="n">
+        <v>891.84382180229</v>
+      </c>
+      <c r="Y39" t="n">
         <v>100.906190368132</v>
       </c>
     </row>
@@ -2044,39 +3471,75 @@
         <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>19</v>
-      </c>
-      <c r="C40" t="n">
+        <v>37</v>
+      </c>
+      <c r="C40" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" t="n">
         <v>0.0272274726873649</v>
       </c>
-      <c r="D40" t="n">
+      <c r="E40" t="n">
         <v>4.52251927826614</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>352.271710132435</v>
       </c>
-      <c r="F40" t="n">
-        <v>314.617363485558</v>
-      </c>
       <c r="G40" t="n">
-        <v>386.985893338926</v>
+        <v>350.131827584382</v>
       </c>
       <c r="H40" t="n">
+        <v>299.113761615382</v>
+      </c>
+      <c r="I40" t="n">
+        <v>402.717896947704</v>
+      </c>
+      <c r="J40" t="n">
+        <v>12412.188979033</v>
+      </c>
+      <c r="K40" t="n">
+        <v>12336.8585383935</v>
+      </c>
+      <c r="L40" t="n">
+        <v>10563.660695039</v>
+      </c>
+      <c r="M40" t="n">
+        <v>14182.3722934696</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2838.11107555243</v>
+      </c>
+      <c r="O40" t="n">
         <v>4137.79993345024</v>
       </c>
-      <c r="I40" t="n">
+      <c r="P40" t="n">
         <v>12.1408452842106</v>
       </c>
-      <c r="J40" t="n">
+      <c r="Q40" t="n">
         <v>12.3001683008809</v>
       </c>
-      <c r="K40" t="n">
-        <v>10.3792257596956</v>
-      </c>
-      <c r="L40" t="n">
-        <v>14.6925250801114</v>
-      </c>
-      <c r="M40" t="n">
+      <c r="R40" t="n">
+        <v>12.1702637351033</v>
+      </c>
+      <c r="S40" t="n">
+        <v>8.39457282520779</v>
+      </c>
+      <c r="T40" t="n">
+        <v>18.0405367058985</v>
+      </c>
+      <c r="U40" t="n">
+        <v>433.392773342624</v>
+      </c>
+      <c r="V40" t="n">
+        <v>429.03395822186</v>
+      </c>
+      <c r="W40" t="n">
+        <v>295.729064199104</v>
+      </c>
+      <c r="X40" t="n">
+        <v>636.106618362713</v>
+      </c>
+      <c r="Y40" t="n">
         <v>100.906190368132</v>
       </c>
     </row>
@@ -2085,39 +3548,75 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>20</v>
-      </c>
-      <c r="C41" t="n">
+        <v>37</v>
+      </c>
+      <c r="C41" t="s">
+        <v>33</v>
+      </c>
+      <c r="D41" t="n">
         <v>0.045058538827935</v>
       </c>
-      <c r="D41" t="n">
+      <c r="E41" t="n">
         <v>3.62093598924897</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>466.753906499165</v>
       </c>
-      <c r="F41" t="n">
-        <v>418.614017179503</v>
-      </c>
       <c r="G41" t="n">
-        <v>513.979074694324</v>
+        <v>469.18431191091</v>
       </c>
       <c r="H41" t="n">
+        <v>408.355279994979</v>
+      </c>
+      <c r="I41" t="n">
+        <v>525.004522469507</v>
+      </c>
+      <c r="J41" t="n">
+        <v>9937.76676542347</v>
+      </c>
+      <c r="K41" t="n">
+        <v>9990.60556921903</v>
+      </c>
+      <c r="L41" t="n">
+        <v>8695.45297276048</v>
+      </c>
+      <c r="M41" t="n">
+        <v>11228.5676461989</v>
+      </c>
+      <c r="N41" t="n">
+        <v>4696.76857503986</v>
+      </c>
+      <c r="O41" t="n">
         <v>4137.79993345024</v>
       </c>
-      <c r="I41" t="n">
+      <c r="P41" t="n">
         <v>15.7071764801393</v>
       </c>
-      <c r="J41" t="n">
+      <c r="Q41" t="n">
         <v>26.3348000670668</v>
       </c>
-      <c r="K41" t="n">
-        <v>22.7089207539869</v>
-      </c>
-      <c r="L41" t="n">
-        <v>29.1830353488043</v>
-      </c>
-      <c r="M41" t="n">
+      <c r="R41" t="n">
+        <v>26.04721787772</v>
+      </c>
+      <c r="S41" t="n">
+        <v>19.0205422858146</v>
+      </c>
+      <c r="T41" t="n">
+        <v>34.4084739517502</v>
+      </c>
+      <c r="U41" t="n">
+        <v>560.700397439601</v>
+      </c>
+      <c r="V41" t="n">
+        <v>554.181782479311</v>
+      </c>
+      <c r="W41" t="n">
+        <v>404.961243904499</v>
+      </c>
+      <c r="X41" t="n">
+        <v>738.051047149082</v>
+      </c>
+      <c r="Y41" t="n">
         <v>100.906190368132</v>
       </c>
     </row>
@@ -2126,39 +3625,75 @@
         <v>50</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
-      </c>
-      <c r="C42" t="n">
+        <v>38</v>
+      </c>
+      <c r="C42" t="s">
+        <v>26</v>
+      </c>
+      <c r="D42" t="n">
         <v>0.401269173435135</v>
       </c>
-      <c r="D42" t="n">
+      <c r="E42" t="n">
         <v>1</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>715.011861244752</v>
       </c>
-      <c r="F42" t="n">
-        <v>771.262366725552</v>
-      </c>
       <c r="G42" t="n">
-        <v>663.188012484006</v>
+        <v>715.318112489319</v>
       </c>
       <c r="H42" t="n">
+        <v>689.205734896872</v>
+      </c>
+      <c r="I42" t="n">
+        <v>741.499245400099</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2390.6932193929</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2391.4989263718</v>
+      </c>
+      <c r="L42" t="n">
+        <v>2303.64438271352</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2478.93809689344</v>
+      </c>
+      <c r="N42" t="n">
+        <v>29908.1394235235</v>
+      </c>
+      <c r="O42" t="n">
         <v>2958.70066977331</v>
       </c>
-      <c r="I42" t="n">
+      <c r="P42" t="n">
         <v>1</v>
       </c>
-      <c r="J42" t="n">
+      <c r="Q42" t="n">
         <v>10.391416832039</v>
       </c>
-      <c r="K42" t="n">
-        <v>13.8588321753461</v>
-      </c>
-      <c r="L42" t="n">
-        <v>7.58994688246539</v>
-      </c>
-      <c r="M42" t="n">
+      <c r="R42" t="n">
+        <v>10.3592743183347</v>
+      </c>
+      <c r="S42" t="n">
+        <v>8.6129850739547</v>
+      </c>
+      <c r="T42" t="n">
+        <v>12.3719866398246</v>
+      </c>
+      <c r="U42" t="n">
+        <v>34.7444442627744</v>
+      </c>
+      <c r="V42" t="n">
+        <v>34.6444631795913</v>
+      </c>
+      <c r="W42" t="n">
+        <v>28.7934287951075</v>
+      </c>
+      <c r="X42" t="n">
+        <v>41.3655018943797</v>
+      </c>
+      <c r="Y42" t="n">
         <v>93.6157214555323</v>
       </c>
     </row>
@@ -2167,39 +3702,75 @@
         <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>14</v>
-      </c>
-      <c r="C43" t="n">
+        <v>38</v>
+      </c>
+      <c r="C43" t="s">
+        <v>27</v>
+      </c>
+      <c r="D43" t="n">
         <v>0.0229898643319388</v>
       </c>
-      <c r="D43" t="n">
+      <c r="E43" t="n">
         <v>1.73620391549785</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>71.1237404915089</v>
       </c>
-      <c r="F43" t="n">
-        <v>68.9879638807515</v>
-      </c>
       <c r="G43" t="n">
-        <v>72.3648704233861</v>
+        <v>71.0384104226498</v>
       </c>
       <c r="H43" t="n">
+        <v>64.7846904979699</v>
+      </c>
+      <c r="I43" t="n">
+        <v>77.2941207958186</v>
+      </c>
+      <c r="J43" t="n">
+        <v>4150.73092826413</v>
+      </c>
+      <c r="K43" t="n">
+        <v>4145.38700234835</v>
+      </c>
+      <c r="L43" t="n">
+        <v>3793.00606684881</v>
+      </c>
+      <c r="M43" t="n">
+        <v>4478.82318437165</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1713.52327386958</v>
+      </c>
+      <c r="O43" t="n">
         <v>2958.70066977331</v>
       </c>
-      <c r="I43" t="n">
+      <c r="P43" t="n">
         <v>3.87720798284478</v>
       </c>
-      <c r="J43" t="n">
+      <c r="Q43" t="n">
         <v>2.30831181964981</v>
       </c>
-      <c r="K43" t="n">
-        <v>2.28197688935607</v>
-      </c>
-      <c r="L43" t="n">
-        <v>2.25019972625052</v>
-      </c>
-      <c r="M43" t="n">
+      <c r="R43" t="n">
+        <v>2.26445739803615</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1.63701396567349</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3.06949457241833</v>
+      </c>
+      <c r="U43" t="n">
+        <v>134.711436655134</v>
+      </c>
+      <c r="V43" t="n">
+        <v>132.038533447358</v>
+      </c>
+      <c r="W43" t="n">
+        <v>95.2609957597881</v>
+      </c>
+      <c r="X43" t="n">
+        <v>179.411049498794</v>
+      </c>
+      <c r="Y43" t="n">
         <v>93.6157214555323</v>
       </c>
     </row>
@@ -2208,39 +3779,75 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
-      </c>
-      <c r="C44" t="n">
+        <v>38</v>
+      </c>
+      <c r="C44" t="s">
+        <v>28</v>
+      </c>
+      <c r="D44" t="n">
         <v>0.399703115252673</v>
       </c>
-      <c r="D44" t="n">
+      <c r="E44" t="n">
         <v>1.52453466418204</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>1085.8061213146</v>
       </c>
-      <c r="F44" t="n">
-        <v>1125.51224588264</v>
-      </c>
       <c r="G44" t="n">
-        <v>1044.43774637443</v>
+        <v>1085.93639451812</v>
       </c>
       <c r="H44" t="n">
+        <v>1045.77722424833</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1126.99367957954</v>
+      </c>
+      <c r="J44" t="n">
+        <v>3644.69468438944</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3645.02915826085</v>
+      </c>
+      <c r="L44" t="n">
+        <v>3510.38051170021</v>
+      </c>
+      <c r="M44" t="n">
+        <v>3782.95239727031</v>
+      </c>
+      <c r="N44" t="n">
+        <v>29791.415065992</v>
+      </c>
+      <c r="O44" t="n">
         <v>2958.70066977331</v>
       </c>
-      <c r="I44" t="n">
+      <c r="P44" t="n">
         <v>2.54503453199424</v>
       </c>
-      <c r="J44" t="n">
+      <c r="Q44" t="n">
         <v>26.3433002147529</v>
       </c>
-      <c r="K44" t="n">
-        <v>29.5433311518452</v>
-      </c>
-      <c r="L44" t="n">
-        <v>22.6449539166386</v>
-      </c>
-      <c r="M44" t="n">
+      <c r="R44" t="n">
+        <v>26.18197400826</v>
+      </c>
+      <c r="S44" t="n">
+        <v>21.9449364076667</v>
+      </c>
+      <c r="T44" t="n">
+        <v>30.960168857899</v>
+      </c>
+      <c r="U44" t="n">
+        <v>88.42581044371</v>
+      </c>
+      <c r="V44" t="n">
+        <v>87.8834446372657</v>
+      </c>
+      <c r="W44" t="n">
+        <v>73.6595366587579</v>
+      </c>
+      <c r="X44" t="n">
+        <v>103.921490127984</v>
+      </c>
+      <c r="Y44" t="n">
         <v>93.6157214555323</v>
       </c>
     </row>
@@ -2249,39 +3856,75 @@
         <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
+        <v>38</v>
+      </c>
+      <c r="C45" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45" t="n">
         <v>0.0255129646858816</v>
       </c>
-      <c r="D45" t="n">
+      <c r="E45" t="n">
         <v>2.89604955563333</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>131.657124610159</v>
       </c>
-      <c r="F45" t="n">
-        <v>118.433310873381</v>
-      </c>
       <c r="G45" t="n">
-        <v>146.602593501829</v>
+        <v>131.642662507273</v>
       </c>
       <c r="H45" t="n">
+        <v>111.482138585077</v>
+      </c>
+      <c r="I45" t="n">
+        <v>152.74306255298</v>
+      </c>
+      <c r="J45" t="n">
+        <v>6923.56603567844</v>
+      </c>
+      <c r="K45" t="n">
+        <v>6923.26065922227</v>
+      </c>
+      <c r="L45" t="n">
+        <v>5886.56742145771</v>
+      </c>
+      <c r="M45" t="n">
+        <v>8051.68526322396</v>
+      </c>
+      <c r="N45" t="n">
+        <v>1901.57967630704</v>
+      </c>
+      <c r="O45" t="n">
         <v>2958.70066977331</v>
       </c>
-      <c r="I45" t="n">
+      <c r="P45" t="n">
         <v>7.90435131698919</v>
       </c>
-      <c r="J45" t="n">
+      <c r="Q45" t="n">
         <v>5.22235188283997</v>
       </c>
-      <c r="K45" t="n">
-        <v>3.74013109663964</v>
-      </c>
-      <c r="L45" t="n">
-        <v>6.79541265643913</v>
-      </c>
-      <c r="M45" t="n">
+      <c r="R45" t="n">
+        <v>5.23496382051011</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.9874172498261</v>
+      </c>
+      <c r="T45" t="n">
+        <v>8.7145046230278</v>
+      </c>
+      <c r="U45" t="n">
+        <v>274.632293766518</v>
+      </c>
+      <c r="V45" t="n">
+        <v>274.900705570969</v>
+      </c>
+      <c r="W45" t="n">
+        <v>157.890562008965</v>
+      </c>
+      <c r="X45" t="n">
+        <v>459.279220913207</v>
+      </c>
+      <c r="Y45" t="n">
         <v>93.6157214555323</v>
       </c>
     </row>
@@ -2290,39 +3933,75 @@
         <v>50</v>
       </c>
       <c r="B46" t="s">
-        <v>17</v>
-      </c>
-      <c r="C46" t="n">
+        <v>38</v>
+      </c>
+      <c r="C46" t="s">
+        <v>30</v>
+      </c>
+      <c r="D46" t="n">
         <v>0.0280986965475078</v>
       </c>
-      <c r="D46" t="n">
+      <c r="E46" t="n">
         <v>2.06769736454035</v>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>103.526277258588</v>
       </c>
-      <c r="F46" t="n">
-        <v>104.078447516122</v>
-      </c>
       <c r="G46" t="n">
-        <v>102.779856172401</v>
+        <v>103.161840135291</v>
       </c>
       <c r="H46" t="n">
+        <v>97.4714097757476</v>
+      </c>
+      <c r="I46" t="n">
+        <v>110.365070961165</v>
+      </c>
+      <c r="J46" t="n">
+        <v>4943.23006916319</v>
+      </c>
+      <c r="K46" t="n">
+        <v>4926.8838368201</v>
+      </c>
+      <c r="L46" t="n">
+        <v>4673.15206330328</v>
+      </c>
+      <c r="M46" t="n">
+        <v>5242.5065419465</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2094.30424661811</v>
+      </c>
+      <c r="O46" t="n">
         <v>2958.70066977331</v>
       </c>
-      <c r="I46" t="n">
+      <c r="P46" t="n">
         <v>5.03462423827642</v>
       </c>
-      <c r="J46" t="n">
+      <c r="Q46" t="n">
         <v>3.66346633664294</v>
       </c>
-      <c r="K46" t="n">
-        <v>3.99084704398186</v>
-      </c>
-      <c r="L46" t="n">
-        <v>3.2655936809998</v>
-      </c>
-      <c r="M46" t="n">
+      <c r="R46" t="n">
+        <v>3.6044049602818</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.94233134530213</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4.45261957057843</v>
+      </c>
+      <c r="U46" t="n">
+        <v>174.925221230808</v>
+      </c>
+      <c r="V46" t="n">
+        <v>172.802354175974</v>
+      </c>
+      <c r="W46" t="n">
+        <v>141.329624045723</v>
+      </c>
+      <c r="X46" t="n">
+        <v>210.806589755083</v>
+      </c>
+      <c r="Y46" t="n">
         <v>93.6157214555323</v>
       </c>
     </row>
@@ -2331,39 +4010,75 @@
         <v>50</v>
       </c>
       <c r="B47" t="s">
-        <v>18</v>
-      </c>
-      <c r="C47" t="n">
+        <v>38</v>
+      </c>
+      <c r="C47" t="s">
+        <v>31</v>
+      </c>
+      <c r="D47" t="n">
         <v>0.00400193847504333</v>
       </c>
-      <c r="D47" t="n">
+      <c r="E47" t="n">
         <v>3.63699661366556</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>25.9352687854643</v>
       </c>
-      <c r="F47" t="n">
-        <v>19.563331136454</v>
-      </c>
       <c r="G47" t="n">
-        <v>33.9250311000385</v>
+        <v>25.8121384423599</v>
       </c>
       <c r="H47" t="n">
+        <v>18.317335701617</v>
+      </c>
+      <c r="I47" t="n">
+        <v>35.7083525830977</v>
+      </c>
+      <c r="J47" t="n">
+        <v>8694.94314324522</v>
+      </c>
+      <c r="K47" t="n">
+        <v>8644.94340878712</v>
+      </c>
+      <c r="L47" t="n">
+        <v>6150.1872182571</v>
+      </c>
+      <c r="M47" t="n">
+        <v>11931.4895039611</v>
+      </c>
+      <c r="N47" t="n">
+        <v>298.279912337465</v>
+      </c>
+      <c r="O47" t="n">
         <v>2958.70066977331</v>
       </c>
-      <c r="I47" t="n">
+      <c r="P47" t="n">
         <v>10.1868679468459</v>
       </c>
-      <c r="J47" t="n">
+      <c r="Q47" t="n">
         <v>1.05572316897591</v>
       </c>
-      <c r="K47" t="n">
-        <v>0.534029426206136</v>
-      </c>
-      <c r="L47" t="n">
-        <v>1.99777667307261</v>
-      </c>
-      <c r="M47" t="n">
+      <c r="R47" t="n">
+        <v>1.04435760939546</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.428911289171824</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.55822269060447</v>
+      </c>
+      <c r="U47" t="n">
+        <v>353.93706559143</v>
+      </c>
+      <c r="V47" t="n">
+        <v>349.578262721931</v>
+      </c>
+      <c r="W47" t="n">
+        <v>145.183395161641</v>
+      </c>
+      <c r="X47" t="n">
+        <v>872.10763972392</v>
+      </c>
+      <c r="Y47" t="n">
         <v>93.6157214555323</v>
       </c>
     </row>
@@ -2372,39 +4087,75 @@
         <v>50</v>
       </c>
       <c r="B48" t="s">
-        <v>19</v>
-      </c>
-      <c r="C48" t="n">
+        <v>38</v>
+      </c>
+      <c r="C48" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" t="n">
         <v>0.0383191660442099</v>
       </c>
-      <c r="D48" t="n">
+      <c r="E48" t="n">
         <v>4.52251927826614</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>308.797605866207</v>
       </c>
-      <c r="F48" t="n">
-        <v>278.357844623244</v>
-      </c>
       <c r="G48" t="n">
-        <v>336.440972791657</v>
+        <v>306.362609028326</v>
       </c>
       <c r="H48" t="n">
+        <v>261.643044276041</v>
+      </c>
+      <c r="I48" t="n">
+        <v>352.290352458469</v>
+      </c>
+      <c r="J48" t="n">
+        <v>10811.9561731245</v>
+      </c>
+      <c r="K48" t="n">
+        <v>10734.1315921464</v>
+      </c>
+      <c r="L48" t="n">
+        <v>9207.25615681128</v>
+      </c>
+      <c r="M48" t="n">
+        <v>12306.9163402456</v>
+      </c>
+      <c r="N48" t="n">
+        <v>2856.07526447241</v>
+      </c>
+      <c r="O48" t="n">
         <v>2958.70066977331</v>
       </c>
-      <c r="I48" t="n">
+      <c r="P48" t="n">
         <v>12.1408452842106</v>
       </c>
-      <c r="J48" t="n">
+      <c r="Q48" t="n">
         <v>12.0476943861307</v>
       </c>
-      <c r="K48" t="n">
-        <v>10.4625783496073</v>
-      </c>
-      <c r="L48" t="n">
-        <v>14.0824806986776</v>
-      </c>
-      <c r="M48" t="n">
+      <c r="R48" t="n">
+        <v>11.8575125639838</v>
+      </c>
+      <c r="S48" t="n">
+        <v>8.20433898519063</v>
+      </c>
+      <c r="T48" t="n">
+        <v>17.6495090527483</v>
+      </c>
+      <c r="U48" t="n">
+        <v>421.826922280224</v>
+      </c>
+      <c r="V48" t="n">
+        <v>415.361026825232</v>
+      </c>
+      <c r="W48" t="n">
+        <v>286.644291730156</v>
+      </c>
+      <c r="X48" t="n">
+        <v>615.687342489542</v>
+      </c>
+      <c r="Y48" t="n">
         <v>93.6157214555323</v>
       </c>
     </row>
@@ -2413,39 +4164,75 @@
         <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>20</v>
-      </c>
-      <c r="C49" t="n">
+        <v>38</v>
+      </c>
+      <c r="C49" t="s">
+        <v>33</v>
+      </c>
+      <c r="D49" t="n">
         <v>0.0801050812276113</v>
       </c>
-      <c r="D49" t="n">
+      <c r="E49" t="n">
         <v>3.62093598924897</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>516.842670202023</v>
       </c>
-      <c r="F49" t="n">
-        <v>472.505159135165</v>
-      </c>
       <c r="G49" t="n">
-        <v>558.961586925559</v>
+        <v>519.27253958655</v>
       </c>
       <c r="H49" t="n">
+        <v>457.152832485991</v>
+      </c>
+      <c r="I49" t="n">
+        <v>577.461234810005</v>
+      </c>
+      <c r="J49" t="n">
+        <v>8656.54711735325</v>
+      </c>
+      <c r="K49" t="n">
+        <v>8695.3624194081</v>
+      </c>
+      <c r="L49" t="n">
+        <v>7651.42992821417</v>
+      </c>
+      <c r="M49" t="n">
+        <v>9684.91753960106</v>
+      </c>
+      <c r="N49" t="n">
+        <v>5970.54071554628</v>
+      </c>
+      <c r="O49" t="n">
         <v>2958.70066977331</v>
       </c>
-      <c r="I49" t="n">
+      <c r="P49" t="n">
         <v>15.7071764801393</v>
       </c>
-      <c r="J49" t="n">
+      <c r="Q49" t="n">
         <v>32.5834568145011</v>
       </c>
-      <c r="K49" t="n">
-        <v>29.2039953225501</v>
-      </c>
-      <c r="L49" t="n">
-        <v>34.9893572209887</v>
-      </c>
-      <c r="M49" t="n">
+      <c r="R49" t="n">
+        <v>32.163230122067</v>
+      </c>
+      <c r="S49" t="n">
+        <v>24.1848375125612</v>
+      </c>
+      <c r="T49" t="n">
+        <v>41.1027661111617</v>
+      </c>
+      <c r="U49" t="n">
+        <v>545.73711773976</v>
+      </c>
+      <c r="V49" t="n">
+        <v>538.836898091531</v>
+      </c>
+      <c r="W49" t="n">
+        <v>406.367931380161</v>
+      </c>
+      <c r="X49" t="n">
+        <v>689.583239733166</v>
+      </c>
+      <c r="Y49" t="n">
         <v>93.6157214555323</v>
       </c>
     </row>
@@ -2454,39 +4241,75 @@
         <v>60</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" t="n">
+        <v>39</v>
+      </c>
+      <c r="C50" t="s">
+        <v>26</v>
+      </c>
+      <c r="D50" t="n">
         <v>0.272748712066189</v>
       </c>
-      <c r="D50" t="n">
+      <c r="E50" t="n">
         <v>1</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>248.780227876054</v>
       </c>
-      <c r="F50" t="n">
-        <v>273.572900790105</v>
-      </c>
       <c r="G50" t="n">
-        <v>226.962390918053</v>
+        <v>249.02590815533</v>
       </c>
       <c r="H50" t="n">
+        <v>236.526814136897</v>
+      </c>
+      <c r="I50" t="n">
+        <v>261.935678884429</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2030.09334194385</v>
+      </c>
+      <c r="K50" t="n">
+        <v>2032.48495129905</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1930.61166090361</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2136.46921554699</v>
+      </c>
+      <c r="N50" t="n">
+        <v>12254.6201564231</v>
+      </c>
+      <c r="O50" t="n">
         <v>1783.54707568208</v>
       </c>
-      <c r="I50" t="n">
+      <c r="P50" t="n">
         <v>1</v>
       </c>
-      <c r="J50" t="n">
+      <c r="Q50" t="n">
         <v>5.40674667364333</v>
       </c>
-      <c r="K50" t="n">
-        <v>7.44957420208927</v>
-      </c>
-      <c r="L50" t="n">
-        <v>3.84277773670801</v>
-      </c>
-      <c r="M50" t="n">
+      <c r="R50" t="n">
+        <v>5.3819307796759</v>
+      </c>
+      <c r="S50" t="n">
+        <v>4.35165592135945</v>
+      </c>
+      <c r="T50" t="n">
+        <v>6.64587680645167</v>
+      </c>
+      <c r="U50" t="n">
+        <v>44.1200674082866</v>
+      </c>
+      <c r="V50" t="n">
+        <v>43.9442987080086</v>
+      </c>
+      <c r="W50" t="n">
+        <v>35.5212266505404</v>
+      </c>
+      <c r="X50" t="n">
+        <v>54.2569303659358</v>
+      </c>
+      <c r="Y50" t="n">
         <v>97.1129506054805</v>
       </c>
     </row>
@@ -2495,39 +4318,75 @@
         <v>60</v>
       </c>
       <c r="B51" t="s">
-        <v>14</v>
-      </c>
-      <c r="C51" t="n">
+        <v>39</v>
+      </c>
+      <c r="C51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D51" t="n">
         <v>0.0143521694697764</v>
       </c>
-      <c r="D51" t="n">
+      <c r="E51" t="n">
         <v>1.73620391549785</v>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>22.7285347065351</v>
       </c>
-      <c r="F51" t="n">
-        <v>22.3407703764747</v>
-      </c>
       <c r="G51" t="n">
-        <v>22.811260736211</v>
+        <v>22.6941097420191</v>
       </c>
       <c r="H51" t="n">
+        <v>20.6183361954319</v>
+      </c>
+      <c r="I51" t="n">
+        <v>24.8293943022935</v>
+      </c>
+      <c r="J51" t="n">
+        <v>3524.65600910904</v>
+      </c>
+      <c r="K51" t="n">
+        <v>3519.16934187655</v>
+      </c>
+      <c r="L51" t="n">
+        <v>3197.56012654824</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3848.8977809234</v>
+      </c>
+      <c r="N51" t="n">
+        <v>644.844054222484</v>
+      </c>
+      <c r="O51" t="n">
         <v>1783.54707568208</v>
       </c>
-      <c r="I51" t="n">
+      <c r="P51" t="n">
         <v>3.87720798284478</v>
       </c>
-      <c r="J51" t="n">
+      <c r="Q51" t="n">
         <v>1.10308750523337</v>
       </c>
-      <c r="K51" t="n">
-        <v>1.11987600481721</v>
-      </c>
-      <c r="L51" t="n">
-        <v>1.04937778562224</v>
-      </c>
-      <c r="M51" t="n">
+      <c r="R51" t="n">
+        <v>1.08857525417161</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0.765574020638621</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1.51493731279079</v>
+      </c>
+      <c r="U51" t="n">
+        <v>171.062677559059</v>
+      </c>
+      <c r="V51" t="n">
+        <v>168.899276274362</v>
+      </c>
+      <c r="W51" t="n">
+        <v>117.252077465289</v>
+      </c>
+      <c r="X51" t="n">
+        <v>232.473536681799</v>
+      </c>
+      <c r="Y51" t="n">
         <v>97.1129506054805</v>
       </c>
     </row>
@@ -2536,39 +4395,75 @@
         <v>60</v>
       </c>
       <c r="B52" t="s">
-        <v>15</v>
-      </c>
-      <c r="C52" t="n">
+        <v>39</v>
+      </c>
+      <c r="C52" t="s">
+        <v>28</v>
+      </c>
+      <c r="D52" t="n">
         <v>0.443512575471991</v>
       </c>
-      <c r="D52" t="n">
+      <c r="E52" t="n">
         <v>1.52453466418204</v>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>616.7318748119</v>
       </c>
-      <c r="F52" t="n">
-        <v>652.036036468398</v>
-      </c>
       <c r="G52" t="n">
-        <v>583.04352845355</v>
+        <v>616.643093414159</v>
       </c>
       <c r="H52" t="n">
+        <v>585.93710222467</v>
+      </c>
+      <c r="I52" t="n">
+        <v>646.801968497502</v>
+      </c>
+      <c r="J52" t="n">
+        <v>3094.94767131857</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3094.50299068474</v>
+      </c>
+      <c r="L52" t="n">
+        <v>2940.96436043901</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3246.45971046931</v>
+      </c>
+      <c r="N52" t="n">
+        <v>19927.0533885682</v>
+      </c>
+      <c r="O52" t="n">
         <v>1783.54707568208</v>
       </c>
-      <c r="I52" t="n">
+      <c r="P52" t="n">
         <v>2.54503453199424</v>
       </c>
-      <c r="J52" t="n">
+      <c r="Q52" t="n">
         <v>22.3755093906441</v>
       </c>
-      <c r="K52" t="n">
-        <v>25.9366998779195</v>
-      </c>
-      <c r="L52" t="n">
-        <v>18.7016170795766</v>
-      </c>
-      <c r="M52" t="n">
+      <c r="R52" t="n">
+        <v>22.214896732953</v>
+      </c>
+      <c r="S52" t="n">
+        <v>17.9391268431553</v>
+      </c>
+      <c r="T52" t="n">
+        <v>27.338990622533</v>
+      </c>
+      <c r="U52" t="n">
+        <v>112.287095108003</v>
+      </c>
+      <c r="V52" t="n">
+        <v>111.497382666828</v>
+      </c>
+      <c r="W52" t="n">
+        <v>90.0190677720969</v>
+      </c>
+      <c r="X52" t="n">
+        <v>137.147251898698</v>
+      </c>
+      <c r="Y52" t="n">
         <v>97.1129506054805</v>
       </c>
     </row>
@@ -2577,39 +4472,75 @@
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
+        <v>39</v>
+      </c>
+      <c r="C53" t="s">
+        <v>29</v>
+      </c>
+      <c r="D53" t="n">
         <v>0.0191946913784536</v>
       </c>
-      <c r="D53" t="n">
+      <c r="E53" t="n">
         <v>2.89604955563333</v>
       </c>
-      <c r="E53" t="n">
+      <c r="F53" t="n">
         <v>50.7037727635333</v>
       </c>
-      <c r="F53" t="n">
-        <v>46.2208308831875</v>
-      </c>
       <c r="G53" t="n">
-        <v>55.6932053027362</v>
+        <v>50.7716202974658</v>
       </c>
       <c r="H53" t="n">
+        <v>42.8725244430351</v>
+      </c>
+      <c r="I53" t="n">
+        <v>59.0796181443161</v>
+      </c>
+      <c r="J53" t="n">
+        <v>5879.25092083068</v>
+      </c>
+      <c r="K53" t="n">
+        <v>5878.15598975722</v>
+      </c>
+      <c r="L53" t="n">
+        <v>4974.06450318847</v>
+      </c>
+      <c r="M53" t="n">
+        <v>6882.12393333105</v>
+      </c>
+      <c r="N53" t="n">
+        <v>862.418927960457</v>
+      </c>
+      <c r="O53" t="n">
         <v>1783.54707568208</v>
       </c>
-      <c r="I53" t="n">
+      <c r="P53" t="n">
         <v>7.90435131698919</v>
       </c>
-      <c r="J53" t="n">
+      <c r="Q53" t="n">
         <v>3.00760419292591</v>
       </c>
-      <c r="K53" t="n">
-        <v>2.21199725096661</v>
-      </c>
-      <c r="L53" t="n">
-        <v>3.8191410121517</v>
-      </c>
-      <c r="M53" t="n">
+      <c r="R53" t="n">
+        <v>3.03216108105664</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1.67071179746877</v>
+      </c>
+      <c r="T53" t="n">
+        <v>5.11132405851532</v>
+      </c>
+      <c r="U53" t="n">
+        <v>348.740512924342</v>
+      </c>
+      <c r="V53" t="n">
+        <v>350.743477957367</v>
+      </c>
+      <c r="W53" t="n">
+        <v>193.468515127284</v>
+      </c>
+      <c r="X53" t="n">
+        <v>590.26612714571</v>
+      </c>
+      <c r="Y53" t="n">
         <v>97.1129506054805</v>
       </c>
     </row>
@@ -2618,39 +4549,75 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>17</v>
-      </c>
-      <c r="C54" t="n">
+        <v>39</v>
+      </c>
+      <c r="C54" t="s">
+        <v>30</v>
+      </c>
+      <c r="D54" t="n">
         <v>0.0318866693879003</v>
       </c>
-      <c r="D54" t="n">
+      <c r="E54" t="n">
         <v>2.06769736454035</v>
       </c>
-      <c r="E54" t="n">
+      <c r="F54" t="n">
         <v>60.1380422515736</v>
       </c>
-      <c r="F54" t="n">
-        <v>61.2671194930228</v>
-      </c>
       <c r="G54" t="n">
-        <v>58.8940396879626</v>
+        <v>59.9661187949087</v>
       </c>
       <c r="H54" t="n">
+        <v>56.0740250113611</v>
+      </c>
+      <c r="I54" t="n">
+        <v>64.5079284886894</v>
+      </c>
+      <c r="J54" t="n">
+        <v>4197.61865290821</v>
+      </c>
+      <c r="K54" t="n">
+        <v>4186.80337306141</v>
+      </c>
+      <c r="L54" t="n">
+        <v>3930.3943120364</v>
+      </c>
+      <c r="M54" t="n">
+        <v>4487.91321151023</v>
+      </c>
+      <c r="N54" t="n">
+        <v>1432.67045494732</v>
+      </c>
+      <c r="O54" t="n">
         <v>1783.54707568208</v>
       </c>
-      <c r="I54" t="n">
+      <c r="P54" t="n">
         <v>5.03462423827642</v>
       </c>
-      <c r="J54" t="n">
+      <c r="Q54" t="n">
         <v>3.18236166610225</v>
       </c>
-      <c r="K54" t="n">
-        <v>3.56012805731993</v>
-      </c>
-      <c r="L54" t="n">
-        <v>2.76831040516458</v>
-      </c>
-      <c r="M54" t="n">
+      <c r="R54" t="n">
+        <v>3.13551355025738</v>
+      </c>
+      <c r="S54" t="n">
+        <v>2.49323577891403</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3.9735018794321</v>
+      </c>
+      <c r="U54" t="n">
+        <v>222.127960768149</v>
+      </c>
+      <c r="V54" t="n">
+        <v>219.031072217595</v>
+      </c>
+      <c r="W54" t="n">
+        <v>175.954807167702</v>
+      </c>
+      <c r="X54" t="n">
+        <v>277.640081506143</v>
+      </c>
+      <c r="Y54" t="n">
         <v>97.1129506054805</v>
       </c>
     </row>
@@ -2659,39 +4626,75 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>18</v>
-      </c>
-      <c r="C55" t="n">
+        <v>39</v>
+      </c>
+      <c r="C55" t="s">
+        <v>31</v>
+      </c>
+      <c r="D55" t="n">
         <v>0.00443456418819989</v>
       </c>
-      <c r="D55" t="n">
+      <c r="E55" t="n">
         <v>3.63699661366556</v>
       </c>
-      <c r="E55" t="n">
+      <c r="F55" t="n">
         <v>14.7111625751475</v>
       </c>
-      <c r="F55" t="n">
-        <v>11.2451956507146</v>
-      </c>
       <c r="G55" t="n">
-        <v>18.9819640564061</v>
+        <v>14.6089862406965</v>
       </c>
       <c r="H55" t="n">
+        <v>10.367674320617</v>
+      </c>
+      <c r="I55" t="n">
+        <v>20.110936716366</v>
+      </c>
+      <c r="J55" t="n">
+        <v>7383.4426100748</v>
+      </c>
+      <c r="K55" t="n">
+        <v>7325.98584437578</v>
+      </c>
+      <c r="L55" t="n">
+        <v>5158.74164639821</v>
+      </c>
+      <c r="M55" t="n">
+        <v>10159.860892417</v>
+      </c>
+      <c r="N55" t="n">
+        <v>199.245302659682</v>
+      </c>
+      <c r="O55" t="n">
         <v>1783.54707568208</v>
       </c>
-      <c r="I55" t="n">
+      <c r="P55" t="n">
         <v>10.1868679468459</v>
       </c>
-      <c r="J55" t="n">
+      <c r="Q55" t="n">
         <v>0.895498649259296</v>
       </c>
-      <c r="K55" t="n">
-        <v>0.465182403412883</v>
-      </c>
-      <c r="L55" t="n">
-        <v>1.65370153327263</v>
-      </c>
-      <c r="M55" t="n">
+      <c r="R55" t="n">
+        <v>0.883050586159563</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0.364498688341773</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2.19575944690827</v>
+      </c>
+      <c r="U55" t="n">
+        <v>449.445300494155</v>
+      </c>
+      <c r="V55" t="n">
+        <v>445.064403157977</v>
+      </c>
+      <c r="W55" t="n">
+        <v>184.268106583812</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1110.05115478806</v>
+      </c>
+      <c r="Y55" t="n">
         <v>97.1129506054805</v>
       </c>
     </row>
@@ -2700,39 +4703,75 @@
         <v>60</v>
       </c>
       <c r="B56" t="s">
-        <v>19</v>
-      </c>
-      <c r="C56" t="n">
+        <v>39</v>
+      </c>
+      <c r="C56" t="s">
+        <v>32</v>
+      </c>
+      <c r="D56" t="n">
         <v>0.0770896898753236</v>
       </c>
-      <c r="D56" t="n">
+      <c r="E56" t="n">
         <v>4.52251927826614</v>
       </c>
-      <c r="E56" t="n">
+      <c r="F56" t="n">
         <v>318.002019592434</v>
       </c>
-      <c r="F56" t="n">
-        <v>293.552793832126</v>
-      </c>
       <c r="G56" t="n">
-        <v>338.843991069962</v>
+        <v>315.63017579199</v>
       </c>
       <c r="H56" t="n">
+        <v>272.878107172428</v>
+      </c>
+      <c r="I56" t="n">
+        <v>359.067117976015</v>
+      </c>
+      <c r="J56" t="n">
+        <v>9181.1362756208</v>
+      </c>
+      <c r="K56" t="n">
+        <v>9116.77609234391</v>
+      </c>
+      <c r="L56" t="n">
+        <v>7893.27658949368</v>
+      </c>
+      <c r="M56" t="n">
+        <v>10356.0336321138</v>
+      </c>
+      <c r="N56" t="n">
+        <v>3463.64556680029</v>
+      </c>
+      <c r="O56" t="n">
         <v>1783.54707568208</v>
       </c>
-      <c r="I56" t="n">
+      <c r="P56" t="n">
         <v>12.1408452842106</v>
       </c>
-      <c r="J56" t="n">
+      <c r="Q56" t="n">
         <v>18.5531876243683</v>
       </c>
-      <c r="K56" t="n">
-        <v>16.7207347030353</v>
-      </c>
-      <c r="L56" t="n">
-        <v>20.9826034070816</v>
-      </c>
-      <c r="M56" t="n">
+      <c r="R56" t="n">
+        <v>18.4053925366938</v>
+      </c>
+      <c r="S56" t="n">
+        <v>12.7353003399418</v>
+      </c>
+      <c r="T56" t="n">
+        <v>26.5694829756364</v>
+      </c>
+      <c r="U56" t="n">
+        <v>535.654912332952</v>
+      </c>
+      <c r="V56" t="n">
+        <v>531.528892272668</v>
+      </c>
+      <c r="W56" t="n">
+        <v>368.002845555518</v>
+      </c>
+      <c r="X56" t="n">
+        <v>765.447805139439</v>
+      </c>
+      <c r="Y56" t="n">
         <v>97.1129506054805</v>
       </c>
     </row>
@@ -2741,39 +4780,75 @@
         <v>60</v>
       </c>
       <c r="B57" t="s">
-        <v>20</v>
-      </c>
-      <c r="C57" t="n">
+        <v>39</v>
+      </c>
+      <c r="C57" t="s">
+        <v>33</v>
+      </c>
+      <c r="D57" t="n">
         <v>0.136780928162167</v>
       </c>
-      <c r="D57" t="n">
+      <c r="E57" t="n">
         <v>3.62093598924897</v>
       </c>
-      <c r="E57" t="n">
+      <c r="F57" t="n">
         <v>451.751441104905</v>
       </c>
-      <c r="F57" t="n">
-        <v>423.311428188053</v>
-      </c>
       <c r="G57" t="n">
-        <v>478.316695457201</v>
+        <v>453.677436997975</v>
       </c>
       <c r="H57" t="n">
+        <v>401.481692650249</v>
+      </c>
+      <c r="I57" t="n">
+        <v>501.318016294568</v>
+      </c>
+      <c r="J57" t="n">
+        <v>7350.83804337921</v>
+      </c>
+      <c r="K57" t="n">
+        <v>7387.04627049714</v>
+      </c>
+      <c r="L57" t="n">
+        <v>6530.32402661482</v>
+      </c>
+      <c r="M57" t="n">
+        <v>8155.65303778913</v>
+      </c>
+      <c r="N57" t="n">
+        <v>6145.57739456374</v>
+      </c>
+      <c r="O57" t="n">
         <v>1783.54707568208</v>
       </c>
-      <c r="I57" t="n">
+      <c r="P57" t="n">
         <v>15.7071764801393</v>
       </c>
-      <c r="J57" t="n">
+      <c r="Q57" t="n">
         <v>42.5889549033039</v>
       </c>
-      <c r="K57" t="n">
-        <v>39.6487581059197</v>
-      </c>
-      <c r="L57" t="n">
-        <v>44.2954216459031</v>
-      </c>
-      <c r="M57" t="n">
+      <c r="R57" t="n">
+        <v>42.114085363482</v>
+      </c>
+      <c r="S57" t="n">
+        <v>32.5072940317636</v>
+      </c>
+      <c r="T57" t="n">
+        <v>52.093677170055</v>
+      </c>
+      <c r="U57" t="n">
+        <v>693.001685097599</v>
+      </c>
+      <c r="V57" t="n">
+        <v>684.225203648124</v>
+      </c>
+      <c r="W57" t="n">
+        <v>529.375950706956</v>
+      </c>
+      <c r="X57" t="n">
+        <v>847.282906607071</v>
+      </c>
+      <c r="Y57" t="n">
         <v>97.1129506054805</v>
       </c>
     </row>
@@ -2782,39 +4857,75 @@
         <v>70</v>
       </c>
       <c r="B58" t="s">
-        <v>13</v>
-      </c>
-      <c r="C58" t="n">
+        <v>40</v>
+      </c>
+      <c r="C58" t="s">
+        <v>26</v>
+      </c>
+      <c r="D58" t="n">
         <v>0.175585465731202</v>
       </c>
-      <c r="D58" t="n">
+      <c r="E58" t="n">
         <v>1</v>
       </c>
-      <c r="E58" t="n">
+      <c r="F58" t="n">
         <v>60.576308819272</v>
       </c>
-      <c r="F58" t="n">
-        <v>67.9282664976479</v>
-      </c>
       <c r="G58" t="n">
-        <v>54.3822855070919</v>
+        <v>60.6931371940478</v>
       </c>
       <c r="H58" t="n">
+        <v>56.5840938168758</v>
+      </c>
+      <c r="I58" t="n">
+        <v>64.9200220846565</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1677.08160691679</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1679.92304666014</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1564.29993409716</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1798.21943468788</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3612.0072254944</v>
+      </c>
+      <c r="O58" t="n">
         <v>816.59643082256</v>
       </c>
-      <c r="I58" t="n">
+      <c r="P58" t="n">
         <v>1</v>
       </c>
-      <c r="J58" t="n">
+      <c r="Q58" t="n">
         <v>2.96646950395381</v>
       </c>
-      <c r="K58" t="n">
-        <v>4.20436200461865</v>
-      </c>
-      <c r="L58" t="n">
-        <v>2.04415627274718</v>
-      </c>
-      <c r="M58" t="n">
+      <c r="R58" t="n">
+        <v>2.9660771057843</v>
+      </c>
+      <c r="S58" t="n">
+        <v>2.26906838296555</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3.74163471241524</v>
+      </c>
+      <c r="U58" t="n">
+        <v>82.1280058083983</v>
+      </c>
+      <c r="V58" t="n">
+        <v>82.1150189712193</v>
+      </c>
+      <c r="W58" t="n">
+        <v>62.6870133267435</v>
+      </c>
+      <c r="X58" t="n">
+        <v>103.310828532061</v>
+      </c>
+      <c r="Y58" t="n">
         <v>107.050517545892</v>
       </c>
     </row>
@@ -2823,39 +4934,75 @@
         <v>70</v>
       </c>
       <c r="B59" t="s">
-        <v>14</v>
-      </c>
-      <c r="C59" t="n">
+        <v>40</v>
+      </c>
+      <c r="C59" t="s">
+        <v>27</v>
+      </c>
+      <c r="D59" t="n">
         <v>0.00887271366221885</v>
       </c>
-      <c r="D59" t="n">
+      <c r="E59" t="n">
         <v>1.73620391549785</v>
       </c>
-      <c r="E59" t="n">
+      <c r="F59" t="n">
         <v>5.31461048593997</v>
       </c>
-      <c r="F59" t="n">
-        <v>5.33338544899872</v>
-      </c>
       <c r="G59" t="n">
-        <v>5.24208791153561</v>
+        <v>5.29786505012981</v>
       </c>
       <c r="H59" t="n">
+        <v>4.772253536671</v>
+      </c>
+      <c r="I59" t="n">
+        <v>5.88284547435635</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2911.75565253836</v>
+      </c>
+      <c r="K59" t="n">
+        <v>2914.1967558006</v>
+      </c>
+      <c r="L59" t="n">
+        <v>2618.24998889804</v>
+      </c>
+      <c r="M59" t="n">
+        <v>3226.99766257554</v>
+      </c>
+      <c r="N59" t="n">
+        <v>182.522543789239</v>
+      </c>
+      <c r="O59" t="n">
         <v>816.59643082256</v>
       </c>
-      <c r="I59" t="n">
+      <c r="P59" t="n">
         <v>3.87720798284478</v>
       </c>
-      <c r="J59" t="n">
+      <c r="Q59" t="n">
         <v>0.581201717110046</v>
       </c>
-      <c r="K59" t="n">
-        <v>0.607667433815591</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0.535367678164301</v>
-      </c>
-      <c r="M59" t="n">
+      <c r="R59" t="n">
+        <v>0.577293075332072</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0.39249367682626</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0.806680510690183</v>
+      </c>
+      <c r="U59" t="n">
+        <v>318.427359735445</v>
+      </c>
+      <c r="V59" t="n">
+        <v>315.002778429007</v>
+      </c>
+      <c r="W59" t="n">
+        <v>214.294078966429</v>
+      </c>
+      <c r="X59" t="n">
+        <v>445.607424098608</v>
+      </c>
+      <c r="Y59" t="n">
         <v>107.050517545892</v>
       </c>
     </row>
@@ -2864,39 +5011,75 @@
         <v>70</v>
       </c>
       <c r="B60" t="s">
-        <v>15</v>
-      </c>
-      <c r="C60" t="n">
+        <v>40</v>
+      </c>
+      <c r="C60" t="s">
+        <v>28</v>
+      </c>
+      <c r="D60" t="n">
         <v>0.417691839140946</v>
       </c>
-      <c r="D60" t="n">
+      <c r="E60" t="n">
         <v>1.52453466418204</v>
       </c>
-      <c r="E60" t="n">
+      <c r="F60" t="n">
         <v>219.688607540263</v>
       </c>
-      <c r="F60" t="n">
-        <v>237.115926137194</v>
-      </c>
       <c r="G60" t="n">
-        <v>204.125210686184</v>
+        <v>219.79201545017</v>
       </c>
       <c r="H60" t="n">
+        <v>205.100795245952</v>
+      </c>
+      <c r="I60" t="n">
+        <v>234.730183617258</v>
+      </c>
+      <c r="J60" t="n">
+        <v>2556.76904440676</v>
+      </c>
+      <c r="K60" t="n">
+        <v>2558.39034944174</v>
+      </c>
+      <c r="L60" t="n">
+        <v>2386.87451743339</v>
+      </c>
+      <c r="M60" t="n">
+        <v>2732.20834055523</v>
+      </c>
+      <c r="N60" t="n">
+        <v>8592.43067029687</v>
+      </c>
+      <c r="O60" t="n">
         <v>816.59643082256</v>
       </c>
-      <c r="I60" t="n">
+      <c r="P60" t="n">
         <v>2.54503453199424</v>
       </c>
-      <c r="J60" t="n">
+      <c r="Q60" t="n">
         <v>17.9597792232586</v>
       </c>
-      <c r="K60" t="n">
-        <v>21.4385317497875</v>
-      </c>
-      <c r="L60" t="n">
-        <v>14.5358387799005</v>
-      </c>
-      <c r="M60" t="n">
+      <c r="R60" t="n">
+        <v>17.8282732652901</v>
+      </c>
+      <c r="S60" t="n">
+        <v>13.8939674416664</v>
+      </c>
+      <c r="T60" t="n">
+        <v>22.6148277081011</v>
+      </c>
+      <c r="U60" t="n">
+        <v>209.018610826197</v>
+      </c>
+      <c r="V60" t="n">
+        <v>207.40740884568</v>
+      </c>
+      <c r="W60" t="n">
+        <v>161.741400448558</v>
+      </c>
+      <c r="X60" t="n">
+        <v>263.15749592098</v>
+      </c>
+      <c r="Y60" t="n">
         <v>107.050517545892</v>
       </c>
     </row>
@@ -2905,39 +5088,75 @@
         <v>70</v>
       </c>
       <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
+        <v>40</v>
+      </c>
+      <c r="C61" t="s">
+        <v>29</v>
+      </c>
+      <c r="D61" t="n">
         <v>0.0194526023069285</v>
       </c>
-      <c r="D61" t="n">
+      <c r="E61" t="n">
         <v>2.89604955563333</v>
       </c>
-      <c r="E61" t="n">
+      <c r="F61" t="n">
         <v>19.4355994256464</v>
       </c>
-      <c r="F61" t="n">
-        <v>18.0884034901158</v>
-      </c>
       <c r="G61" t="n">
-        <v>20.9804542417808</v>
+        <v>19.4595677121569</v>
       </c>
       <c r="H61" t="n">
+        <v>16.4358130730346</v>
+      </c>
+      <c r="I61" t="n">
+        <v>22.748150227392</v>
+      </c>
+      <c r="J61" t="n">
+        <v>4856.9114424722</v>
+      </c>
+      <c r="K61" t="n">
+        <v>4849.19605851981</v>
+      </c>
+      <c r="L61" t="n">
+        <v>4127.29450519222</v>
+      </c>
+      <c r="M61" t="n">
+        <v>5672.40520128774</v>
+      </c>
+      <c r="N61" t="n">
+        <v>400.163759538378</v>
+      </c>
+      <c r="O61" t="n">
         <v>816.59643082256</v>
       </c>
-      <c r="I61" t="n">
+      <c r="P61" t="n">
         <v>7.90435131698919</v>
       </c>
-      <c r="J61" t="n">
+      <c r="Q61" t="n">
         <v>2.5977375190137</v>
       </c>
-      <c r="K61" t="n">
-        <v>1.96760658681534</v>
-      </c>
-      <c r="L61" t="n">
-        <v>3.19406417255606</v>
-      </c>
-      <c r="M61" t="n">
+      <c r="R61" t="n">
+        <v>2.61475041537086</v>
+      </c>
+      <c r="S61" t="n">
+        <v>1.42061912193615</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4.48224837766752</v>
+      </c>
+      <c r="U61" t="n">
+        <v>649.16861087331</v>
+      </c>
+      <c r="V61" t="n">
+        <v>653.468749505466</v>
+      </c>
+      <c r="W61" t="n">
+        <v>355.189009018496</v>
+      </c>
+      <c r="X61" t="n">
+        <v>1129.01730279575</v>
+      </c>
+      <c r="Y61" t="n">
         <v>107.050517545892</v>
       </c>
     </row>
@@ -2946,39 +5165,75 @@
         <v>70</v>
       </c>
       <c r="B62" t="s">
-        <v>17</v>
-      </c>
-      <c r="C62" t="n">
+        <v>40</v>
+      </c>
+      <c r="C62" t="s">
+        <v>30</v>
+      </c>
+      <c r="D62" t="n">
         <v>0.0333496674189622</v>
       </c>
-      <c r="D62" t="n">
+      <c r="E62" t="n">
         <v>2.06769736454035</v>
       </c>
-      <c r="E62" t="n">
+      <c r="F62" t="n">
         <v>23.7899058836241</v>
       </c>
-      <c r="F62" t="n">
-        <v>24.7443314862175</v>
-      </c>
       <c r="G62" t="n">
-        <v>22.8965364595847</v>
+        <v>23.7557891680157</v>
       </c>
       <c r="H62" t="n">
+        <v>21.9523744188632</v>
+      </c>
+      <c r="I62" t="n">
+        <v>25.8347017350671</v>
+      </c>
+      <c r="J62" t="n">
+        <v>3467.69721874093</v>
+      </c>
+      <c r="K62" t="n">
+        <v>3462.98562680316</v>
+      </c>
+      <c r="L62" t="n">
+        <v>3207.66564924017</v>
+      </c>
+      <c r="M62" t="n">
+        <v>3770.64310936206</v>
+      </c>
+      <c r="N62" t="n">
+        <v>686.043341819268</v>
+      </c>
+      <c r="O62" t="n">
         <v>816.59643082256</v>
       </c>
-      <c r="I62" t="n">
+      <c r="P62" t="n">
         <v>5.03462423827642</v>
       </c>
-      <c r="J62" t="n">
+      <c r="Q62" t="n">
         <v>2.8366770413098</v>
       </c>
-      <c r="K62" t="n">
-        <v>3.26817330760326</v>
-      </c>
-      <c r="L62" t="n">
-        <v>2.38934301986583</v>
-      </c>
-      <c r="M62" t="n">
+      <c r="R62" t="n">
+        <v>2.78772989504792</v>
+      </c>
+      <c r="S62" t="n">
+        <v>2.16552895658802</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3.6230718787207</v>
+      </c>
+      <c r="U62" t="n">
+        <v>413.483648684269</v>
+      </c>
+      <c r="V62" t="n">
+        <v>405.7093352256</v>
+      </c>
+      <c r="W62" t="n">
+        <v>317.255878296816</v>
+      </c>
+      <c r="X62" t="n">
+        <v>524.016230714079</v>
+      </c>
+      <c r="Y62" t="n">
         <v>107.050517545892</v>
       </c>
     </row>
@@ -2987,39 +5242,75 @@
         <v>70</v>
       </c>
       <c r="B63" t="s">
-        <v>18</v>
-      </c>
-      <c r="C63" t="n">
+        <v>40</v>
+      </c>
+      <c r="C63" t="s">
+        <v>31</v>
+      </c>
+      <c r="D63" t="n">
         <v>0.00501331582198318</v>
       </c>
-      <c r="D63" t="n">
+      <c r="E63" t="n">
         <v>3.63699661366556</v>
       </c>
-      <c r="E63" t="n">
+      <c r="F63" t="n">
         <v>6.29045708307122</v>
       </c>
-      <c r="F63" t="n">
-        <v>4.90915844644441</v>
-      </c>
       <c r="G63" t="n">
-        <v>7.97684888302297</v>
+        <v>6.24247948362625</v>
       </c>
       <c r="H63" t="n">
+        <v>4.43738833892778</v>
+      </c>
+      <c r="I63" t="n">
+        <v>8.68427149898279</v>
+      </c>
+      <c r="J63" t="n">
+        <v>6099.54012519716</v>
+      </c>
+      <c r="K63" t="n">
+        <v>6031.58117043687</v>
+      </c>
+      <c r="L63" t="n">
+        <v>4287.29557462486</v>
+      </c>
+      <c r="M63" t="n">
+        <v>8487.17414484623</v>
+      </c>
+      <c r="N63" t="n">
+        <v>103.130022164874</v>
+      </c>
+      <c r="O63" t="n">
         <v>816.59643082256</v>
       </c>
-      <c r="I63" t="n">
+      <c r="P63" t="n">
         <v>10.1868679468459</v>
       </c>
-      <c r="J63" t="n">
+      <c r="Q63" t="n">
         <v>0.86281376513742</v>
       </c>
-      <c r="K63" t="n">
-        <v>0.461587997766377</v>
-      </c>
-      <c r="L63" t="n">
-        <v>1.5428106114057</v>
-      </c>
-      <c r="M63" t="n">
+      <c r="R63" t="n">
+        <v>0.860070714593069</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0.349547858767753</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2.17519715542897</v>
+      </c>
+      <c r="U63" t="n">
+        <v>836.627149907946</v>
+      </c>
+      <c r="V63" t="n">
+        <v>836.164165920257</v>
+      </c>
+      <c r="W63" t="n">
+        <v>342.109652954672</v>
+      </c>
+      <c r="X63" t="n">
+        <v>2115.18033543047</v>
+      </c>
+      <c r="Y63" t="n">
         <v>107.050517545892</v>
       </c>
     </row>
@@ -3028,39 +5319,75 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>19</v>
-      </c>
-      <c r="C64" t="n">
+        <v>40</v>
+      </c>
+      <c r="C64" t="s">
+        <v>32</v>
+      </c>
+      <c r="D64" t="n">
         <v>0.182376623362917</v>
       </c>
-      <c r="D64" t="n">
+      <c r="E64" t="n">
         <v>4.52251927826614</v>
       </c>
-      <c r="E64" t="n">
+      <c r="F64" t="n">
         <v>284.55343979875</v>
       </c>
-      <c r="F64" t="n">
-        <v>269.747952553479</v>
-      </c>
       <c r="G64" t="n">
-        <v>296.424554293457</v>
+        <v>282.907540400665</v>
       </c>
       <c r="H64" t="n">
+        <v>251.58867072527</v>
+      </c>
+      <c r="I64" t="n">
+        <v>313.53882947352</v>
+      </c>
+      <c r="J64" t="n">
+        <v>7584.63389850672</v>
+      </c>
+      <c r="K64" t="n">
+        <v>7543.08293692777</v>
+      </c>
+      <c r="L64" t="n">
+        <v>6717.85042061184</v>
+      </c>
+      <c r="M64" t="n">
+        <v>8346.51734145774</v>
+      </c>
+      <c r="N64" t="n">
+        <v>3751.70962246146</v>
+      </c>
+      <c r="O64" t="n">
         <v>816.59643082256</v>
       </c>
-      <c r="I64" t="n">
+      <c r="P64" t="n">
         <v>12.1408452842106</v>
       </c>
-      <c r="J64" t="n">
+      <c r="Q64" t="n">
         <v>37.4084246546653</v>
       </c>
-      <c r="K64" t="n">
-        <v>34.9235586573757</v>
-      </c>
-      <c r="L64" t="n">
-        <v>40.7510712142913</v>
-      </c>
-      <c r="M64" t="n">
+      <c r="R64" t="n">
+        <v>37.2128535579078</v>
+      </c>
+      <c r="S64" t="n">
+        <v>27.1898159158916</v>
+      </c>
+      <c r="T64" t="n">
+        <v>49.5476402235456</v>
+      </c>
+      <c r="U64" t="n">
+        <v>997.103412020517</v>
+      </c>
+      <c r="V64" t="n">
+        <v>991.336985160558</v>
+      </c>
+      <c r="W64" t="n">
+        <v>723.561524096268</v>
+      </c>
+      <c r="X64" t="n">
+        <v>1319.42515156822</v>
+      </c>
+      <c r="Y64" t="n">
         <v>107.050517545892</v>
       </c>
     </row>
@@ -3069,39 +5396,75 @@
         <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>20</v>
-      </c>
-      <c r="C65" t="n">
+        <v>40</v>
+      </c>
+      <c r="C65" t="s">
+        <v>33</v>
+      </c>
+      <c r="D65" t="n">
         <v>0.157657772554841</v>
       </c>
-      <c r="D65" t="n">
+      <c r="E65" t="n">
         <v>3.62093598924897</v>
       </c>
-      <c r="E65" t="n">
+      <c r="F65" t="n">
         <v>196.947501785993</v>
       </c>
-      <c r="F65" t="n">
-        <v>188.729006762463</v>
-      </c>
       <c r="G65" t="n">
-        <v>204.568452839904</v>
+        <v>198.047361321602</v>
       </c>
       <c r="H65" t="n">
+        <v>172.239654792332</v>
+      </c>
+      <c r="I65" t="n">
+        <v>221.383204302237</v>
+      </c>
+      <c r="J65" t="n">
+        <v>6072.60514739249</v>
+      </c>
+      <c r="K65" t="n">
+        <v>6106.3740278412</v>
+      </c>
+      <c r="L65" t="n">
+        <v>5343.76691070846</v>
+      </c>
+      <c r="M65" t="n">
+        <v>6820.6160713447</v>
+      </c>
+      <c r="N65" t="n">
+        <v>3243.2127069971</v>
+      </c>
+      <c r="O65" t="n">
         <v>816.59643082256</v>
       </c>
-      <c r="I65" t="n">
+      <c r="P65" t="n">
         <v>15.7071764801393</v>
       </c>
-      <c r="J65" t="n">
+      <c r="Q65" t="n">
         <v>41.8374141214432</v>
       </c>
-      <c r="K65" t="n">
-        <v>40.1790298081095</v>
-      </c>
-      <c r="L65" t="n">
-        <v>42.0578657969611</v>
-      </c>
-      <c r="M65" t="n">
+      <c r="R65" t="n">
+        <v>41.4013000702343</v>
+      </c>
+      <c r="S65" t="n">
+        <v>30.8559637244139</v>
+      </c>
+      <c r="T65" t="n">
+        <v>52.8219628497313</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1289.99908119442</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1276.15443509727</v>
+      </c>
+      <c r="W65" t="n">
+        <v>958.878509938261</v>
+      </c>
+      <c r="X65" t="n">
+        <v>1628.3101469073</v>
+      </c>
+      <c r="Y65" t="n">
         <v>107.050517545892</v>
       </c>
     </row>
@@ -3110,39 +5473,75 @@
         <v>80</v>
       </c>
       <c r="B66" t="s">
-        <v>13</v>
-      </c>
-      <c r="C66" t="n">
-        <v>0.109797933787815</v>
+        <v>41</v>
+      </c>
+      <c r="C66" t="s">
+        <v>26</v>
       </c>
       <c r="D66" t="n">
+        <v>0.117015895132005</v>
+      </c>
+      <c r="E66" t="n">
         <v>1</v>
       </c>
-      <c r="E66" t="n">
-        <v>11.7800429010395</v>
-      </c>
       <c r="F66" t="n">
-        <v>13.3538090442138</v>
+        <v>12.9742779574223</v>
       </c>
       <c r="G66" t="n">
-        <v>10.4901116161657</v>
+        <v>13.0134800791489</v>
       </c>
       <c r="H66" t="n">
+        <v>11.8224764020052</v>
+      </c>
+      <c r="I66" t="n">
+        <v>14.2271730409589</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1398.61664508684</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1403.16815338292</v>
+      </c>
+      <c r="L66" t="n">
+        <v>1278.29164756755</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1531.04831575354</v>
+      </c>
+      <c r="N66" t="n">
+        <v>927.650761414806</v>
+      </c>
+      <c r="O66" t="n">
         <v>314.692995970824</v>
       </c>
-      <c r="I66" t="n">
+      <c r="P66" t="n">
         <v>1</v>
       </c>
-      <c r="J66" t="n">
-        <v>1.21809586305134</v>
-      </c>
-      <c r="K66" t="n">
-        <v>1.75558337715611</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0.820230303264637</v>
-      </c>
-      <c r="M66" t="n">
+      <c r="Q66" t="n">
+        <v>1.34071880476239</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1.33641531862496</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0.972350550129251</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1.74563705840296</v>
+      </c>
+      <c r="U66" t="n">
+        <v>144.528400183448</v>
+      </c>
+      <c r="V66" t="n">
+        <v>143.888684463483</v>
+      </c>
+      <c r="W66" t="n">
+        <v>104.337585889663</v>
+      </c>
+      <c r="X66" t="n">
+        <v>188.242187054871</v>
+      </c>
+      <c r="Y66" t="n">
         <v>89.4656556238432</v>
       </c>
     </row>
@@ -3151,39 +5550,75 @@
         <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>14</v>
-      </c>
-      <c r="C67" t="n">
-        <v>0.00258229384098748</v>
+        <v>41</v>
+      </c>
+      <c r="C67" t="s">
+        <v>27</v>
       </c>
       <c r="D67" t="n">
+        <v>0.00292617054001268</v>
+      </c>
+      <c r="E67" t="n">
         <v>1.73620391549785</v>
       </c>
-      <c r="E67" t="n">
-        <v>0.481015526824659</v>
-      </c>
       <c r="F67" t="n">
-        <v>0.456857944078502</v>
+        <v>0.563298641247376</v>
       </c>
       <c r="G67" t="n">
-        <v>0.502351098456357</v>
+        <v>0.56179731065805</v>
       </c>
       <c r="H67" t="n">
+        <v>0.475383467337512</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.657325532070188</v>
+      </c>
+      <c r="J67" t="n">
+        <v>2428.28369548025</v>
+      </c>
+      <c r="K67" t="n">
+        <v>2427.59711325877</v>
+      </c>
+      <c r="L67" t="n">
+        <v>2145.88811101136</v>
+      </c>
+      <c r="M67" t="n">
+        <v>2740.56865743015</v>
+      </c>
+      <c r="N67" t="n">
+        <v>23.1973983227677</v>
+      </c>
+      <c r="O67" t="n">
         <v>314.692995970824</v>
       </c>
-      <c r="I67" t="n">
+      <c r="P67" t="n">
         <v>3.87720798284478</v>
       </c>
-      <c r="J67" t="n">
-        <v>0.111073909565412</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0.11056327615239</v>
-      </c>
-      <c r="L67" t="n">
-        <v>0.106722076539208</v>
-      </c>
-      <c r="M67" t="n">
+      <c r="Q67" t="n">
+        <v>0.129990487797868</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0.128535861356869</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0.0843909451194859</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0.191529212854316</v>
+      </c>
+      <c r="U67" t="n">
+        <v>560.366666939049</v>
+      </c>
+      <c r="V67" t="n">
+        <v>555.053260622327</v>
+      </c>
+      <c r="W67" t="n">
+        <v>367.078060522321</v>
+      </c>
+      <c r="X67" t="n">
+        <v>811.69711353432</v>
+      </c>
+      <c r="Y67" t="n">
         <v>89.4656556238432</v>
       </c>
     </row>
@@ -3192,39 +5627,75 @@
         <v>80</v>
       </c>
       <c r="B68" t="s">
-        <v>15</v>
-      </c>
-      <c r="C68" t="n">
-        <v>0.332002297006316</v>
+        <v>41</v>
+      </c>
+      <c r="C68" t="s">
+        <v>28</v>
       </c>
       <c r="D68" t="n">
+        <v>0.351327667773727</v>
+      </c>
+      <c r="E68" t="n">
         <v>1.52453466418204</v>
       </c>
-      <c r="E68" t="n">
-        <v>54.303909471094</v>
-      </c>
       <c r="F68" t="n">
-        <v>60.0431832946267</v>
+        <v>59.3865361791903</v>
       </c>
       <c r="G68" t="n">
-        <v>49.4670584114859</v>
+        <v>59.4789643560079</v>
       </c>
       <c r="H68" t="n">
+        <v>54.1982439990157</v>
+      </c>
+      <c r="I68" t="n">
+        <v>65.3364356661486</v>
+      </c>
+      <c r="J68" t="n">
+        <v>2132.23955733688</v>
+      </c>
+      <c r="K68" t="n">
+        <v>2135.18751465283</v>
+      </c>
+      <c r="L68" t="n">
+        <v>1945.88235124475</v>
+      </c>
+      <c r="M68" t="n">
+        <v>2345.64313505134</v>
+      </c>
+      <c r="N68" t="n">
+        <v>2785.17186189729</v>
+      </c>
+      <c r="O68" t="n">
         <v>314.692995970824</v>
       </c>
-      <c r="I68" t="n">
+      <c r="P68" t="n">
         <v>2.54503453199424</v>
       </c>
-      <c r="J68" t="n">
-        <v>9.37393782349781</v>
-      </c>
-      <c r="K68" t="n">
-        <v>11.5309410117635</v>
-      </c>
-      <c r="L68" t="n">
-        <v>7.32754678015507</v>
-      </c>
-      <c r="M68" t="n">
+      <c r="Q68" t="n">
+        <v>10.2446912348035</v>
+      </c>
+      <c r="R68" t="n">
+        <v>10.1449171245442</v>
+      </c>
+      <c r="S68" t="n">
+        <v>7.58248240761362</v>
+      </c>
+      <c r="T68" t="n">
+        <v>13.4471396825742</v>
+      </c>
+      <c r="U68" t="n">
+        <v>367.829769320757</v>
+      </c>
+      <c r="V68" t="n">
+        <v>364.218656906749</v>
+      </c>
+      <c r="W68" t="n">
+        <v>272.271011373358</v>
+      </c>
+      <c r="X68" t="n">
+        <v>482.682242977896</v>
+      </c>
+      <c r="Y68" t="n">
         <v>89.4656556238432</v>
       </c>
     </row>
@@ -3233,39 +5704,75 @@
         <v>80</v>
       </c>
       <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>0.0133067234726806</v>
+        <v>41</v>
+      </c>
+      <c r="C69" t="s">
+        <v>29</v>
       </c>
       <c r="D69" t="n">
+        <v>0.0134536203710678</v>
+      </c>
+      <c r="E69" t="n">
         <v>2.89604955563333</v>
       </c>
-      <c r="E69" t="n">
-        <v>4.13456501485343</v>
-      </c>
       <c r="F69" t="n">
-        <v>3.64185522389625</v>
+        <v>4.31999751004355</v>
       </c>
       <c r="G69" t="n">
-        <v>4.72565675525049</v>
+        <v>4.34533011954966</v>
       </c>
       <c r="H69" t="n">
+        <v>3.50792915183601</v>
+      </c>
+      <c r="I69" t="n">
+        <v>5.28697209095036</v>
+      </c>
+      <c r="J69" t="n">
+        <v>4050.46311350514</v>
+      </c>
+      <c r="K69" t="n">
+        <v>4055.88239923325</v>
+      </c>
+      <c r="L69" t="n">
+        <v>3407.23513824411</v>
+      </c>
+      <c r="M69" t="n">
+        <v>4771.60588383009</v>
+      </c>
+      <c r="N69" t="n">
+        <v>106.654409359753</v>
+      </c>
+      <c r="O69" t="n">
         <v>314.692995970824</v>
       </c>
-      <c r="I69" t="n">
+      <c r="P69" t="n">
         <v>7.90435131698919</v>
       </c>
-      <c r="J69" t="n">
-        <v>1.16687589201695</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0.841448295953621</v>
-      </c>
-      <c r="L69" t="n">
-        <v>1.49654571268097</v>
-      </c>
-      <c r="M69" t="n">
+      <c r="Q69" t="n">
+        <v>1.21842343914861</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1.2116760353088</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0.655966336219273</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2.23593452336799</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1142.40325033238</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1142.47618591472</v>
+      </c>
+      <c r="W69" t="n">
+        <v>618.97833435981</v>
+      </c>
+      <c r="X69" t="n">
+        <v>2031.0966135767</v>
+      </c>
+      <c r="Y69" t="n">
         <v>89.4656556238432</v>
       </c>
     </row>
@@ -3274,39 +5781,75 @@
         <v>80</v>
       </c>
       <c r="B70" t="s">
-        <v>17</v>
-      </c>
-      <c r="C70" t="n">
-        <v>0.0166686361403016</v>
+        <v>41</v>
+      </c>
+      <c r="C70" t="s">
+        <v>30</v>
       </c>
       <c r="D70" t="n">
+        <v>0.0182448144531161</v>
+      </c>
+      <c r="E70" t="n">
         <v>2.06769736454035</v>
       </c>
-      <c r="E70" t="n">
-        <v>3.69776872767248</v>
-      </c>
       <c r="F70" t="n">
-        <v>3.64009988143844</v>
+        <v>4.18277750724134</v>
       </c>
       <c r="G70" t="n">
-        <v>3.768184982002</v>
+        <v>4.18631108671486</v>
       </c>
       <c r="H70" t="n">
+        <v>3.62683453305151</v>
+      </c>
+      <c r="I70" t="n">
+        <v>4.83697721329117</v>
+      </c>
+      <c r="J70" t="n">
+        <v>2891.91595104833</v>
+      </c>
+      <c r="K70" t="n">
+        <v>2896.17503769556</v>
+      </c>
+      <c r="L70" t="n">
+        <v>2614.17764830284</v>
+      </c>
+      <c r="M70" t="n">
+        <v>3186.43292353661</v>
+      </c>
+      <c r="N70" t="n">
+        <v>144.63689740793</v>
+      </c>
+      <c r="O70" t="n">
         <v>314.692995970824</v>
       </c>
-      <c r="I70" t="n">
+      <c r="P70" t="n">
         <v>5.03462423827642</v>
       </c>
-      <c r="J70" t="n">
-        <v>0.931010179519141</v>
-      </c>
-      <c r="K70" t="n">
-        <v>1.02119665023471</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0.817974919598426</v>
-      </c>
-      <c r="M70" t="n">
+      <c r="Q70" t="n">
+        <v>1.05244486852526</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1.04263417769987</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0.754454970714705</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1.39098956856022</v>
+      </c>
+      <c r="U70" t="n">
+        <v>727.6461866829</v>
+      </c>
+      <c r="V70" t="n">
+        <v>719.235115112186</v>
+      </c>
+      <c r="W70" t="n">
+        <v>529.473100065145</v>
+      </c>
+      <c r="X70" t="n">
+        <v>967.519408757494</v>
+      </c>
+      <c r="Y70" t="n">
         <v>89.4656556238432</v>
       </c>
     </row>
@@ -3315,39 +5858,75 @@
         <v>80</v>
       </c>
       <c r="B71" t="s">
-        <v>18</v>
-      </c>
-      <c r="C71" t="n">
-        <v>0.00278528881526836</v>
+        <v>41</v>
+      </c>
+      <c r="C71" t="s">
+        <v>31</v>
       </c>
       <c r="D71" t="n">
+        <v>0.00297693726612225</v>
+      </c>
+      <c r="E71" t="n">
         <v>3.63699661366556</v>
       </c>
-      <c r="E71" t="n">
-        <v>1.0868405572617</v>
-      </c>
       <c r="F71" t="n">
-        <v>0.802751704436351</v>
+        <v>1.2004689129236</v>
       </c>
       <c r="G71" t="n">
-        <v>1.45925234033341</v>
+        <v>1.20029612937631</v>
       </c>
       <c r="H71" t="n">
+        <v>0.838984635966471</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1.69375014061502</v>
+      </c>
+      <c r="J71" t="n">
+        <v>5086.76400199714</v>
+      </c>
+      <c r="K71" t="n">
+        <v>5043.61681641563</v>
+      </c>
+      <c r="L71" t="n">
+        <v>3569.26837057743</v>
+      </c>
+      <c r="M71" t="n">
+        <v>7198.39587447929</v>
+      </c>
+      <c r="N71" t="n">
+        <v>23.599854690571</v>
+      </c>
+      <c r="O71" t="n">
         <v>314.692995970824</v>
       </c>
-      <c r="I71" t="n">
+      <c r="P71" t="n">
         <v>10.1868679468459</v>
       </c>
-      <c r="J71" t="n">
-        <v>0.314773535710621</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0.160322849087286</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0.587098152603773</v>
-      </c>
-      <c r="M71" t="n">
+      <c r="Q71" t="n">
+        <v>0.34745870824939</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0.353465018015907</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0.136571678271878</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0.881880903877407</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1472.29172723768</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1482.1139271264</v>
+      </c>
+      <c r="W71" t="n">
+        <v>583.061051853606</v>
+      </c>
+      <c r="X71" t="n">
+        <v>3793.33541306932</v>
+      </c>
+      <c r="Y71" t="n">
         <v>89.4656556238432</v>
       </c>
     </row>
@@ -3356,39 +5935,75 @@
         <v>80</v>
       </c>
       <c r="B72" t="s">
-        <v>19</v>
-      </c>
-      <c r="C72" t="n">
-        <v>0.373073157399231</v>
+        <v>41</v>
+      </c>
+      <c r="C72" t="s">
+        <v>32</v>
       </c>
       <c r="D72" t="n">
+        <v>0.337267378784898</v>
+      </c>
+      <c r="E72" t="n">
         <v>4.52251927826614</v>
       </c>
-      <c r="E72" t="n">
-        <v>181.020239056726</v>
-      </c>
       <c r="F72" t="n">
-        <v>176.101296804689</v>
+        <v>169.119272934312</v>
       </c>
       <c r="G72" t="n">
-        <v>184.630934110125</v>
+        <v>168.505174809129</v>
       </c>
       <c r="H72" t="n">
+        <v>154.833295723535</v>
+      </c>
+      <c r="I72" t="n">
+        <v>181.30064507685</v>
+      </c>
+      <c r="J72" t="n">
+        <v>6325.27074030916</v>
+      </c>
+      <c r="K72" t="n">
+        <v>6301.17885736118</v>
+      </c>
+      <c r="L72" t="n">
+        <v>5791.03696351169</v>
+      </c>
+      <c r="M72" t="n">
+        <v>6770.63114319118</v>
+      </c>
+      <c r="N72" t="n">
+        <v>2673.70804946834</v>
+      </c>
+      <c r="O72" t="n">
         <v>314.692995970824</v>
       </c>
-      <c r="I72" t="n">
+      <c r="P72" t="n">
         <v>12.1408452842106</v>
       </c>
-      <c r="J72" t="n">
-        <v>50.2493245285972</v>
-      </c>
-      <c r="K72" t="n">
-        <v>48.4272285918349</v>
-      </c>
-      <c r="L72" t="n">
-        <v>52.7993265919626</v>
-      </c>
-      <c r="M72" t="n">
+      <c r="Q72" t="n">
+        <v>46.9154734836758</v>
+      </c>
+      <c r="R72" t="n">
+        <v>46.7535054823485</v>
+      </c>
+      <c r="S72" t="n">
+        <v>36.547034591169</v>
+      </c>
+      <c r="T72" t="n">
+        <v>57.450532264501</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1754.69694580172</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1749.28478375518</v>
+      </c>
+      <c r="W72" t="n">
+        <v>1368.45898039534</v>
+      </c>
+      <c r="X72" t="n">
+        <v>2149.48113421908</v>
+      </c>
+      <c r="Y72" t="n">
         <v>89.4656556238432</v>
       </c>
     </row>
@@ -3397,39 +6012,75 @@
         <v>80</v>
       </c>
       <c r="B73" t="s">
-        <v>20</v>
-      </c>
-      <c r="C73" t="n">
-        <v>0.1497836695374</v>
+        <v>41</v>
+      </c>
+      <c r="C73" t="s">
+        <v>33</v>
       </c>
       <c r="D73" t="n">
+        <v>0.156787515679052</v>
+      </c>
+      <c r="E73" t="n">
         <v>3.62093598924897</v>
       </c>
-      <c r="E73" t="n">
-        <v>58.1886147153524</v>
-      </c>
       <c r="F73" t="n">
-        <v>56.6531420734453</v>
+        <v>62.9463663284441</v>
       </c>
       <c r="G73" t="n">
-        <v>59.6494466570055</v>
+        <v>63.3053149925856</v>
       </c>
       <c r="H73" t="n">
+        <v>54.3718509438743</v>
+      </c>
+      <c r="I73" t="n">
+        <v>71.9661736565414</v>
+      </c>
+      <c r="J73" t="n">
+        <v>5064.3013453576</v>
+      </c>
+      <c r="K73" t="n">
+        <v>5094.40480408859</v>
+      </c>
+      <c r="L73" t="n">
+        <v>4362.13283940988</v>
+      </c>
+      <c r="M73" t="n">
+        <v>5798.01327011044</v>
+      </c>
+      <c r="N73" t="n">
+        <v>1242.94274838417</v>
+      </c>
+      <c r="O73" t="n">
         <v>314.692995970824</v>
       </c>
-      <c r="I73" t="n">
+      <c r="P73" t="n">
         <v>15.7071764801393</v>
       </c>
-      <c r="J73" t="n">
-        <v>26.1005638918848</v>
-      </c>
-      <c r="K73" t="n">
-        <v>25.6183715716607</v>
-      </c>
-      <c r="L73" t="n">
-        <v>25.5102110870385</v>
-      </c>
-      <c r="M73" t="n">
+      <c r="Q73" t="n">
+        <v>28.2164545968805</v>
+      </c>
+      <c r="R73" t="n">
+        <v>27.9327314034334</v>
+      </c>
+      <c r="S73" t="n">
+        <v>19.7272543336278</v>
+      </c>
+      <c r="T73" t="n">
+        <v>37.74301265544</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2270.13308807361</v>
+      </c>
+      <c r="V73" t="n">
+        <v>2246.72065536127</v>
+      </c>
+      <c r="W73" t="n">
+        <v>1593.42746358892</v>
+      </c>
+      <c r="X73" t="n">
+        <v>3028.90148146073</v>
+      </c>
+      <c r="Y73" t="n">
         <v>89.4656556238432</v>
       </c>
     </row>
